--- a/output/2026-09_품목신고보고현황.xlsx
+++ b/output/2026-09_품목신고보고현황.xlsx
@@ -7631,7 +7631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I193"/>
+  <dimension ref="A1:I195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10045,7 +10045,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20180545231163</t>
+          <t>20180545231164</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>표고버섯 분말</t>
+          <t>abc주스분말</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -10075,24 +10075,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>건표고버섯</t>
+          <t>사과분말, 당근분말, 레드비트분말</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20180545231164</t>
+          <t>20180545231163</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>abc주스분말</t>
+          <t>표고버섯 분말</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>사과분말, 당근분말, 레드비트분말</t>
+          <t>건표고버섯</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11220,7 +11220,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260559122148</t>
+          <t>20260559122151</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>틈틈 멜라코어드림</t>
+          <t>티어밸런스</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -11250,24 +11250,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>테아닌, 식품첨가물, 기타 농산가공품, 기타가공품, 합성향료(4-Aminobutyric acid), L-트립토판, 과.채가공품, 기타가공품, 기타가공품, 산화마그네슘, 이산화규소, 스테아린산마그네슘, 산화아연, 혼합제제, 혼합제제, 비타민B6염산염, 엽산</t>
+          <t>기타가공품, 혼합제제, 스테아린산마그네슘, 이산화규소, 유청칼슘, 과.채가공품, 기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260559122151</t>
+          <t>20260559122148</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>티어밸런스</t>
+          <t>틈틈 멜라코어드림</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -11297,17 +11297,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>기타가공품, 혼합제제, 스테아린산마그네슘, 이산화규소, 유청칼슘, 과.채가공품, 기타가공품, 기타가공품</t>
+          <t>테아닌, 식품첨가물, 기타 농산가공품, 기타가공품, 합성향료(4-Aminobutyric acid), L-트립토판, 과.채가공품, 기타가공품, 기타가공품, 산화마그네슘, 이산화규소, 스테아린산마그네슘, 산화아연, 혼합제제, 혼합제제, 비타민B6염산염, 엽산</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -11831,7 +11831,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20090415087203</t>
+          <t>20090415087204</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DB효소</t>
+          <t>SH효소</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -11861,12 +11861,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>곡류혼합분말, 식물혼합추출물, 유산균혼합배양액</t>
+          <t>곡류혼합, 식물혼합추출물, 유산균혼합배양액</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11878,7 +11878,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20090415087204</t>
+          <t>20090415087203</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SH효소</t>
+          <t>DB효소</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>곡류혼합, 식물혼합추출물, 유산균혼합배양액</t>
+          <t>곡류혼합분말, 식물혼합추출물, 유산균혼합배양액</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -12912,7 +12912,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>202202738571304</t>
+          <t>202202738571300</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>파라다이스그레인 자보티카바 올인원 포뮬러</t>
+          <t>리체르카 식물성 멜라토닌 함유 2mg</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -12942,24 +12942,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>과.채가공품, 결정셀룰로스, 덱스트린, 올리고당, 기타가공품, 과.채가공품, α-시클로덱스트린, 기타가공품, 효모식품, 기타가공품, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품, 과.채가공품, 과.채가공품, 기타가공품, 산화아연, 테아닌, 이산화규소, 스테아린산마그네슘, 과.채가공품, 기타가공품, 기타 농산가공품</t>
+          <t>기타가공품, 과.채가공품, 과.채가공품, 가바, 기타가공품, 테아닌, L-트립토판, 기타가공품, 고형차, 기타가공품, 산화아연, 산화마그네슘, 이산화규소, 스테아린산마그네슘, 혼합제제, 비타민B6염산염</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>다이어트</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>20220495001358</t>
+          <t>202202738571304</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12969,44 +12969,44 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20220495001</t>
+          <t>20220273857</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>디엔에이 조이셀</t>
+          <t>파라다이스그레인 자보티카바 올인원 포뮬러</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>(주)한미양행 선유공장</t>
+          <t>(주)네이처코퍼레이션</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>포도당, 유함유가공품, 레시틴, L-아르지닌, 과.채가공품, 비타민C, L-카르니틴, 산화마그네슘, 기타가공품, NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 니코틴산아미드, 산화아연, 비타민B1염산염, 혼합제제, 비타민B6염산염, 혼합제제, 기타가공품, 효모식품, 과.채가공품, 비타민B2, 프로바이오틱스(고시형), 올리고당, 기타가공품, 기타가공품, 과.채가공품, 엽산, 혼합제제</t>
+          <t>과.채가공품, 결정셀룰로스, 덱스트린, 올리고당, 기타가공품, 과.채가공품, α-시클로덱스트린, 기타가공품, 효모식품, 기타가공품, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품, 과.채가공품, 과.채가공품, 기타가공품, 산화아연, 테아닌, 이산화규소, 스테아린산마그네슘, 과.채가공품, 기타가공품, 기타 농산가공품</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>다이어트</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>20220495001355</t>
+          <t>20220495001358</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>촘촘 콜라겐 비오틴</t>
+          <t>디엔에이 조이셀</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -13041,19 +13041,19 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>기타가공품, 버터유, 글리신, 과.채가공품, 혼합제제, 기타가공품, 포도당, 비타민C, 과.채가공품, 혼합제제, 당류가공품, 기타 농산가공품, 자일리톨, DL-사과산, 과.채가공품, 니코틴산아미드, 효모식품, 수크랄로스, 비오틴, 프로바이오틱스(고시형), 히알루론산</t>
+          <t>포도당, 유함유가공품, 레시틴, L-아르지닌, 과.채가공품, 비타민C, L-카르니틴, 산화마그네슘, 기타가공품, NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 니코틴산아미드, 산화아연, 비타민B1염산염, 혼합제제, 비타민B6염산염, 혼합제제, 기타가공품, 효모식품, 과.채가공품, 비타민B2, 프로바이오틱스(고시형), 올리고당, 기타가공품, 기타가공품, 과.채가공품, 엽산, 혼합제제</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>모발</t>
+          <t>관절</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>20220495001356</t>
+          <t>20220495001359</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>굿앤굿 타트체리 스틱</t>
+          <t>피쉬콜라겐 석류맛</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -13083,24 +13083,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>자일리톨, 비타민C, D-소비톨, 혼합제제, 기타 농산가공품, 구연산(무수), 당류가공품, 올리고당, 이산화규소, DL-사과산, 효소처리스테비아, 히알루론산, 올리고당, 포도당, 에리스리톨, 과.채가공품</t>
+          <t>히알루론산, 프로바이오틱스(고시형), 수크랄로스, 비타민B2, 비타민B1염산염, 과.채가공품, 과.채가공품, 이산화규소, 스테아린산마그네슘, 기타가공품, 포도당, 비타민C, 올리고당, 당류가공품, 혼합제제, 과.채가공품, 자일리톨</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>20220495001357</t>
+          <t>20220495001355</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>당돌한 발효여주</t>
+          <t>촘촘 콜라겐 비오틴</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -13135,19 +13135,19 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>기타가공품, 기타가공품</t>
+          <t>기타가공품, 버터유, 글리신, 과.채가공품, 혼합제제, 기타가공품, 포도당, 비타민C, 과.채가공품, 혼합제제, 당류가공품, 기타 농산가공품, 자일리톨, DL-사과산, 과.채가공품, 니코틴산아미드, 효모식품, 수크랄로스, 비오틴, 프로바이오틱스(고시형), 히알루론산</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>모발</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>20220495001359</t>
+          <t>20220495001356</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>피쉬콜라겐 석류맛</t>
+          <t>굿앤굿 타트체리 스틱</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -13182,19 +13182,19 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>히알루론산, 프로바이오틱스(고시형), 수크랄로스, 비타민B2, 비타민B1염산염, 과.채가공품, 과.채가공품, 이산화규소, 스테아린산마그네슘, 기타가공품, 포도당, 비타민C, 올리고당, 당류가공품, 혼합제제, 과.채가공품, 자일리톨</t>
+          <t>자일리톨, 비타민C, D-소비톨, 혼합제제, 기타 농산가공품, 구연산(무수), 당류가공품, 올리고당, 이산화규소, DL-사과산, 효소처리스테비아, 히알루론산, 올리고당, 포도당, 에리스리톨, 과.채가공품</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2022088812230</t>
+          <t>20220495001357</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13204,12 +13204,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>20220888122</t>
+          <t>20220495001</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>닥터엔오 요리수</t>
+          <t>당돌한 발효여주</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -13219,29 +13219,29 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>주식회사 늘다</t>
+          <t>(주)한미양행 선유공장</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>정제수, 천일염, 액상차</t>
+          <t>기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20230528144356</t>
+          <t>2022088812230</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20220888122</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>하루 마그네슘</t>
+          <t>닥터엔오 요리수</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -13266,17 +13266,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>주식회사 늘다</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>포도당, 자일리톨, 글루콘산마그네슘, 파인애플농축, 파인애플향분말, 파인애플맛분말, 이산화규소, 구연산(무수), L-젖산마그네슘, 효소처리스테비아, DL-사과산</t>
+          <t>정제수, 천일염, 액상차</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -13288,7 +13288,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>20230517987169</t>
+          <t>20230528144356</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13298,12 +13298,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>20230517987</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 프리미엄 복합물</t>
+          <t>하루 마그네슘</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>(주)디에스푸드웰 화성지점</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>과.채가공품, 결정셀룰로스, 덱스트린, 과.채가공품, 기타 농산가공품</t>
+          <t>포도당, 자일리톨, 글루콘산마그네슘, 파인애플농축, 파인애플향분말, 파인애플맛분말, 이산화규소, 구연산(무수), L-젖산마그네슘, 효소처리스테비아, DL-사과산</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -13335,7 +13335,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>20230517987170</t>
+          <t>20230517987169</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>날마다 씬나게 양춘사 바나바잎 맥스</t>
+          <t>파라다이스 그레인 프리미엄 복합물</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -13370,19 +13370,19 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>고형차, 바나바잎 추출물(고시형), 난소화성말토덱스트린(고시형), 효모식품, 판토텐산칼슘, 스테아린산마그네슘, 이산화규소, 비타민B2, 비타민B1염산염, 비오틴</t>
+          <t>과.채가공품, 결정셀룰로스, 덱스트린, 과.채가공품, 기타 농산가공품</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>모발</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>20230517987171</t>
+          <t>20230517987170</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>알파CD 프리미엄 복합물</t>
+          <t>날마다 씬나게 양춘사 바나바잎 맥스</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>D-소비톨, α-시클로덱스트린, 난소화성말토덱스트린(고시형), 기타 농산가공품</t>
+          <t>고형차, 바나바잎 추출물(고시형), 난소화성말토덱스트린(고시형), 효모식품, 판토텐산칼슘, 스테아린산마그네슘, 이산화규소, 비타민B2, 비타민B1염산염, 비오틴</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>다이어트</t>
+          <t>모발</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -13476,7 +13476,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>20230612332337</t>
+          <t>20230517987171</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13486,22 +13486,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>20230612332</t>
+          <t>20230517987</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>진자이효소</t>
+          <t>알파CD 프리미엄 복합물</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>(주)웰레스트</t>
+          <t>(주)디에스푸드웰 화성지점</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>과.채가공품, α-시클로덱스트린, 히비스커스꽃받침추출분말, 치커리뿌리추출물분말, 레몬밤추출물, 핑거루트뿌리, 흑삼분말, 스테아린산마그네슘, DL-사과산, 토마토추출물분말, D-소비톨, 구연산(무수), 병풀추출, 파인애플과즙분말, 파파야추출분말, 식품첨가물, 파인애플향분말, 파인애플맛분말, 포도당, 테아닌, 니코틴산아미드, 식품첨가물혼합제제</t>
+          <t>D-소비톨, α-시클로덱스트린, 난소화성말토덱스트린(고시형), 기타 농산가공품</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -13523,7 +13523,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2024068305729</t>
+          <t>20230612332337</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>20240683057</t>
+          <t>20230612332</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>톡소365클렌즈</t>
+          <t>진자이효소</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>케이바이오젠주식회사</t>
+          <t>(주)웰레스트</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -13558,19 +13558,19 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>마카농축액분말, 사과농축액, 덱스트린, 식물혼합추출물, 프락토올리고당, 기타가공품, L-아르지닌, 타우린, 식용누에고치단백가수분해물분말, 비타민C, 구연산(무수), N-아세틸글루코사민분말, 황금추출물, 천연향료(Civet(Zibeth, Zibet, Zibetum)), 석류농축액, 겨우살이농축추출물분말, 산화아연, 효소처리스테비아, 라디아타소나무나무껍질, 두류가공품, 판토텐산칼슘, 초유분말, 비타민B1염산염, 비타민B6염산염, 비타민B2, l-멘톨, 엽산</t>
+          <t>과.채가공품, α-시클로덱스트린, 히비스커스꽃받침추출분말, 치커리뿌리추출물분말, 레몬밤추출물, 핑거루트뿌리, 흑삼분말, 스테아린산마그네슘, DL-사과산, 토마토추출물분말, D-소비톨, 구연산(무수), 병풀추출, 파인애플과즙분말, 파파야추출분말, 식품첨가물, 파인애플향분말, 파인애플맛분말, 포도당, 테아닌, 니코틴산아미드, 식품첨가물혼합제제</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>다이어트</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2024063505422</t>
+          <t>2024068305729</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13580,22 +13580,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>20240635054</t>
+          <t>20240683057</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>헛개나무열매농축액</t>
+          <t>톡소365클렌즈</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>주식회사 비에스바이오</t>
+          <t>케이바이오젠주식회사</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -13605,19 +13605,19 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>헛개나무열매농축액</t>
+          <t>마카농축액분말, 사과농축액, 덱스트린, 식물혼합추출물, 프락토올리고당, 기타가공품, L-아르지닌, 타우린, 식용누에고치단백가수분해물분말, 비타민C, 구연산(무수), N-아세틸글루코사민분말, 황금추출물, 천연향료(Civet(Zibeth, Zibet, Zibetum)), 석류농축액, 겨우살이농축추출물분말, 산화아연, 효소처리스테비아, 라디아타소나무나무껍질, 두류가공품, 판토텐산칼슘, 초유분말, 비타민B1염산염, 비타민B6염산염, 비타민B2, l-멘톨, 엽산</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>관절</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>202409566354</t>
+          <t>2024063505422</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13627,44 +13627,44 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>20240956635</t>
+          <t>20240635054</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>제주크래프트콜라에너지젤 아르기닌</t>
+          <t>헛개나무열매농축액</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>제주크래프트콜라</t>
+          <t>주식회사 비에스바이오</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L-아르지닌, 한천, 정제수, 콜라원액 A</t>
+          <t>헛개나무열매농축액</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>202409566353</t>
+          <t>202409566354</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>제주크래프트콜라에너지젤 타우린</t>
+          <t>제주크래프트콜라에너지젤 아르기닌</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>타우린, 한천, 정제수, 콜라원액 A</t>
+          <t>L-아르지닌, 한천, 정제수, 콜라원액 A</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -13711,7 +13711,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025022612834</t>
+          <t>202409566353</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13721,44 +13721,44 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>20250226128</t>
+          <t>20240956635</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>리틀포레스트(Little Forest)</t>
+          <t>제주크래프트콜라에너지젤 타우린</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>주식회사 센비아</t>
+          <t>제주크래프트콜라</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>감귤, 오렌지, 에둘리스시계꽃열매, 레몬, 설탕, 사탕수수가루</t>
+          <t>타우린, 한천, 정제수, 콜라원액 A</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>202605933617</t>
+          <t>2025022612834</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -13768,22 +13768,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>20260593361</t>
+          <t>20250226128</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>소프트요 요거트플레인파우더</t>
+          <t>리틀포레스트(Little Forest)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>한국프레나</t>
+          <t>주식회사 센비아</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>백설탕, 요거트분말, 분말결정포도당, 탈지분유, 덱스트린, 구연산(무수), 요구르트향분말, 구아검, DL-사과산, 카복시메틸셀룰로스나트륨, 결정셀룰로스, 비타민C</t>
+          <t>감귤, 오렌지, 에둘리스시계꽃열매, 레몬, 설탕, 사탕수수가루</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -13805,7 +13805,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>202605933616</t>
+          <t>202605933617</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>마이요거트립 요거트파우더</t>
+          <t>소프트요 요거트플레인파우더</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>요거트분말, 백설탕, 분말결정포도당, 탈지분유, 덱스트린, 구연산(무수), 요구르트향분말, 구아검, DL-사과산, 카복시메틸셀룰로스나트륨, 결정셀룰로스, 비타민C</t>
+          <t>백설탕, 요거트분말, 분말결정포도당, 탈지분유, 덱스트린, 구연산(무수), 요구르트향분말, 구아검, DL-사과산, 카복시메틸셀룰로스나트륨, 결정셀룰로스, 비타민C</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -13852,7 +13852,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>202605933618</t>
+          <t>202605933616</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>녹차아이스크림파우더</t>
+          <t>마이요거트립 요거트파우더</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>정제소금, 아라비아검, 카복시메틸셀룰로스나트륨, 탈지분유, 유당, 버터유분말, 전지분유, 녹차가루, 유청분말, 덱스트린, 식물성크림, 백설탕</t>
+          <t>요거트분말, 백설탕, 분말결정포도당, 탈지분유, 덱스트린, 구연산(무수), 요구르트향분말, 구아검, DL-사과산, 카복시메틸셀룰로스나트륨, 결정셀룰로스, 비타민C</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -13899,7 +13899,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>20260559122153</t>
+          <t>202605933618</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -13909,32 +13909,32 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>20260559122</t>
+          <t>20260593361</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>테토닉스</t>
+          <t>녹차아이스크림파우더</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>(주)코스모바이오</t>
+          <t>한국프레나</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>식품첨가물, 기타가공품, 고형차, 포도당, L-아르지닌, 과.채가공품, 기타가공품, 혼합제제, 혼합제제, 비타민C, 비타민B6염산염, 기타가공품, 이산화규소, 스테아린산마그네슘</t>
+          <t>정제소금, 아라비아검, 카복시메틸셀룰로스나트륨, 탈지분유, 유당, 버터유분말, 전지분유, 녹차가루, 유청분말, 덱스트린, 식물성크림, 백설탕</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -13946,7 +13946,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>20260559122154</t>
+          <t>20260559122153</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>양춘사 바나바잎 정</t>
+          <t>테토닉스</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -13976,24 +13976,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>고형차, 기타가공품, 효소식품, 이산화규소, 스테아린산마그네슘, 건조효모, 비타민B1염산염, 고형차</t>
+          <t>식품첨가물, 기타가공품, 고형차, 포도당, L-아르지닌, 과.채가공품, 기타가공품, 혼합제제, 혼합제제, 비타민C, 비타민B6염산염, 기타가공품, 이산화규소, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>20260559122157</t>
+          <t>20260559122154</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>자보티카바 베리 정</t>
+          <t>양춘사 바나바잎 정</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14028,34 +14028,34 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>과.채가공품, 과.채가공품, 식품첨가물, 과.채가공품, 기타가공품, 과.채가공품, 혼합제제, 비타민C, 이산화규소, 스테아린산마그네슘</t>
+          <t>고형차, 기타가공품, 효소식품, 이산화규소, 스테아린산마그네슘, 건조효모, 비타민B1염산염, 고형차</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>198604350131749</t>
+          <t>20260559122157</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>19860435013</t>
+          <t>20260559122</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EONER파이토그린포뮬러</t>
+          <t>자보티카바 베리 정</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>코스맥스바이오(주)</t>
+          <t>(주)코스모바이오</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>과.채가공품, 사과과즙분말, 치커리추출분말, 밀식이섬유(고시형)</t>
+          <t>과.채가공품, 과.채가공품, 식품첨가물, 과.채가공품, 기타가공품, 과.채가공품, 혼합제제, 비타민C, 이산화규소, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -14087,7 +14087,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>19870364007343</t>
+          <t>198604350131749</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -14097,44 +14097,44 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>19870364007</t>
+          <t>19860435013</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>유산균배양액</t>
+          <t>EONER파이토그린포뮬러</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>(주)보락</t>
+          <t>코스맥스바이오(주)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>쌀눈, 효모추출물, 백설탕, L-글루탐산나트륨, 황산망간, 황산마그네슘, 제이인산칼륨, 정제수, Latilactobacillus sakei, 비타민B6염산염</t>
+          <t>과.채가공품, 사과과즙분말, 치커리추출분말, 밀식이섬유(고시형)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>199003720871008</t>
+          <t>19870364007343</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -14144,22 +14144,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>19900372087</t>
+          <t>19870364007</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>100% 유기농 레드와인 비니거</t>
+          <t>유산균배양액</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>(주)화인내츄럴</t>
+          <t>(주)보락</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -14169,19 +14169,19 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>쌀눈, 효모추출물, 백설탕, L-글루탐산나트륨, 황산망간, 황산마그네슘, 제이인산칼륨, 정제수, Latilactobacillus sakei, 비타민B6염산염</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>프로바이오틱스</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>19910464049639</t>
+          <t>199003720871008</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14191,44 +14191,44 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>19910464049</t>
+          <t>19900372087</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>납작복숭아시럽-J</t>
+          <t>100% 유기농 레드와인 비니거</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>(주)프레시코</t>
+          <t>(주)화인내츄럴</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>올리고당가공품, 정제수, 복사나무열매농축액, 향료, 향료, 향료, 향료, 향료, 구연산, 복사나무열매퓨레, 펙틴, 산화아연, 혼합제제, 기타가공품</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>19940474147418</t>
+          <t>19910464049639</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14238,32 +14238,32 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>19940474147</t>
+          <t>19910464049</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>홍자몽펄프</t>
+          <t>납작복숭아시럽-J</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>주식회사 예산농산</t>
+          <t>(주)프레시코</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>과.채가공품, 설탕, 정제수</t>
+          <t>올리고당가공품, 정제수, 복사나무열매농축액, 향료, 향료, 향료, 향료, 향료, 구연산, 복사나무열매퓨레, 펙틴, 산화아연, 혼합제제, 기타가공품</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -14275,7 +14275,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>200303950191023</t>
+          <t>19940474147418</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14285,12 +14285,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>20030395019</t>
+          <t>19940474147</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>페이퍼백 오버나이트 밸런스</t>
+          <t>홍자몽펄프</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -14300,29 +14300,29 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>(주)유유헬스케어</t>
+          <t>주식회사 예산농산</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>히알루론산, 히드록시프로필메틸셀룰로스, 글리세린지방산에스테르, 체리추출물, 산화마그네슘, L-트립토판, 결정셀룰로스, 혼합제제, 카복시메틸셀룰로스칼슘, 니코틴산아미드, 이산화규소, 스테아린산마그네슘, 비타민B12혼합제제분말, 비타민B6염산염, 엽산, L-테아닌(고시형), 기타가공품, 이노시톨, 캐모마일추출물분말, 기타가공품, 생선콜라겐</t>
+          <t>과.채가공품, 설탕, 정제수</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>200504490252183</t>
+          <t>200303950191023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -14332,12 +14332,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>20050449025</t>
+          <t>20030395019</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>발효자몽농축분말SR-30248</t>
+          <t>페이퍼백 오버나이트 밸런스</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -14347,29 +14347,29 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>주식회사새롬비앤에프농업회사법인</t>
+          <t>(주)유유헬스케어</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>덱스트린, 유산균음료</t>
+          <t>히알루론산, 히드록시프로필메틸셀룰로스, 글리세린지방산에스테르, 체리추출물, 산화마그네슘, L-트립토판, 결정셀룰로스, 혼합제제, 카복시메틸셀룰로스칼슘, 니코틴산아미드, 이산화규소, 스테아린산마그네슘, 비타민B12혼합제제분말, 비타민B6염산염, 엽산, L-테아닌(고시형), 기타가공품, 이노시톨, 캐모마일추출물분말, 기타가공품, 생선콜라겐</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>200603644661204</t>
+          <t>200504490252183</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -14379,22 +14379,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>20060364466</t>
+          <t>20050449025</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>에프엔어니스티 염지제</t>
+          <t>발효자몽농축분말SR-30248</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>(주)청정두리</t>
+          <t>주식회사새롬비앤에프농업회사법인</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -14404,19 +14404,19 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>복합조미식품, 과.채가공품, 기타가공품, 향신료조제품, 전분, 포도당, 식품첨가물혼합제제, 기타가공품, 카레, 설탕, L-글루탐산나트륨, 정제소금, 향료, 올레오레진 캪시컴, 식품첨가물, 올레오레진 블랙페퍼, 향료</t>
+          <t>덱스트린, 유산균음료</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>프로바이오틱스</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>20060415215392</t>
+          <t>200603644661204</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -14426,12 +14426,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>20060415215</t>
+          <t>20060364466</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>유산균 발효 가수분해 양태반</t>
+          <t>에프엔어니스티 염지제</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -14441,29 +14441,29 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>주식회사 노바렉스 2공장</t>
+          <t>(주)청정두리</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>정제수, D-소비톨액, 양태반추출물</t>
+          <t>복합조미식품, 과.채가공품, 기타가공품, 향신료조제품, 전분, 포도당, 식품첨가물혼합제제, 기타가공품, 카레, 설탕, L-글루탐산나트륨, 정제소금, 향료, 올레오레진 캪시컴, 식품첨가물, 올레오레진 블랙페퍼, 향료</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>20070309132920</t>
+          <t>20060415215392</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -14473,44 +14473,44 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>20070309132</t>
+          <t>20060415215</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>흑염소진액 골드</t>
+          <t>유산균 발효 가수분해 양태반</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>(주)코리아화인에프티</t>
+          <t>주식회사 노바렉스 2공장</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>흑염소혼합추출액, 프락토올리고당, 당류가공품, 잔탄검, 향료, 인삼열매농축액, 기타가공품, 비타민C</t>
+          <t>정제수, D-소비톨액, 양태반추출물</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>프로바이오틱스</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>20090555025160</t>
+          <t>20070309132920</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -14520,44 +14520,44 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>20090555025</t>
+          <t>20070309132</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>국내산당근착즙액</t>
+          <t>흑염소진액 골드</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>(주)보성식품</t>
+          <t>(주)코리아화인에프티</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>당근</t>
+          <t>흑염소혼합추출액, 프락토올리고당, 당류가공품, 잔탄검, 향료, 인삼열매농축액, 기타가공품, 비타민C</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2009046720491</t>
+          <t>20090555025160</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -14567,44 +14567,44 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>20090467204</t>
+          <t>20090555025</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>유기농 레드와인 비니거 스틱</t>
+          <t>국내산당근착즙액</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>(주)믿음의나무 농업회사법인</t>
+          <t>(주)보성식품</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>당근</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2011037013558</t>
+          <t>2009046720491</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -14614,44 +14614,44 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>20110370135</t>
+          <t>20090467204</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>포그랜드 림보 포그캔디(FOGLANDLIMBO Fog Candy)</t>
+          <t>유기농 레드와인 비니거 스틱</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>다산식품</t>
+          <t>(주)믿음의나무 농업회사법인</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>식용색소청색제1호, l-멘톨, 사이다향, 박하유, 물엿, 백설탕</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>201104490151150</t>
+          <t>2011037013558</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -14661,32 +14661,32 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>20110449015</t>
+          <t>20110370135</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>아토자임 락토</t>
+          <t>포그랜드 림보 포그캔디(FOGLANDLIMBO Fog Candy)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>주식회사오투바이오</t>
+          <t>다산식품</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>벌꿀분말, 감귤향분말, 감귤농축분말, 건조효모, 쌀발효분말, 포도당, 에리스리톨, 구연산, L-아스파라진, 헛개나무추출물분말, 비타민 C(고시형), 유채유, 효소처리스테비아, 자당지방산에스테르, 니코틴산아미드, 비타민A혼합분말, 생선콜라겐</t>
+          <t>식용색소청색제1호, l-멘톨, 사이다향, 박하유, 물엿, 백설탕</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -14698,7 +14698,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>20110372457670</t>
+          <t>201104490151150</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -14708,12 +14708,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>20110372457</t>
+          <t>20110449015</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>링티 나잇티</t>
+          <t>아토자임 락토</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>자연그대로(주)</t>
+          <t>주식회사오투바이오</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -14733,19 +14733,19 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>과.채가공품, 자일리톨, 에리스리톨, DL-사과산, 기타가공품, 산화마그네슘(고시형), 향료, 구연산(무수), 과.채가공품, 스테비올배당체, 수크랄로스, 효소식품, 테아닌, L-트립토판, 기타가공품, 비타민B6염산염혼합제제, 비타민B12, 혼합제제</t>
+          <t>벌꿀분말, 감귤향분말, 감귤농축분말, 건조효모, 쌀발효분말, 포도당, 에리스리톨, 구연산, L-아스파라진, 헛개나무추출물분말, 비타민 C(고시형), 유채유, 효소처리스테비아, 자당지방산에스테르, 니코틴산아미드, 비타민A혼합분말, 생선콜라겐</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>20120364578466</t>
+          <t>20110372457670</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14755,12 +14755,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>20120364578</t>
+          <t>20110372457</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>수향현미양송이스프</t>
+          <t>링티 나잇티</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -14770,29 +14770,29 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>가온식품</t>
+          <t>자연그대로(주)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>현미가루, 생크림, 전지분유, 백설탕, 정제소금, 옥수수가루, 양송이플레이크, 양파분말, 감자전분, 후추가루, 효모추출물</t>
+          <t>과.채가공품, 자일리톨, 에리스리톨, DL-사과산, 기타가공품, 산화마그네슘(고시형), 향료, 구연산(무수), 과.채가공품, 스테비올배당체, 수크랄로스, 효소식품, 테아닌, L-트립토판, 기타가공품, 비타민B6염산염혼합제제, 비타민B12, 혼합제제</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>20120046517677</t>
+          <t>20120364578466</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14802,12 +14802,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>20120046517</t>
+          <t>20120364578</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>읍성닭강정 전용파우더</t>
+          <t>수향현미양송이스프</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -14817,17 +14817,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>(주)아이엠소스</t>
+          <t>가온식품</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L-글루탐산나트륨, 정제소금, 변성전분, 산화전분, 옥수수전분, 밀가루, 콩기름(대두유), 구아검, 포도당, 천연향신료, 천연향신료, 식품첨가물, 천연향신료, 양파분말, 고춧가루, 탄산칼슘, 베이킹파우더, 탄산수소나트륨</t>
+          <t>현미가루, 생크림, 전지분유, 백설탕, 정제소금, 옥수수가루, 양송이플레이크, 양파분말, 감자전분, 후추가루, 효모추출물</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -14839,7 +14839,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2014055607581</t>
+          <t>20120046517677</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14849,32 +14849,32 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>20140556075</t>
+          <t>20120046517</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>사과오리진비니거</t>
+          <t>읍성닭강정 전용파우더</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>농업회사법인 주식회사 초마루</t>
+          <t>(주)아이엠소스</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>사과, 정제수, 설탕, 효모</t>
+          <t>L-글루탐산나트륨, 정제소금, 변성전분, 산화전분, 옥수수전분, 밀가루, 콩기름(대두유), 구아검, 포도당, 천연향신료, 천연향신료, 식품첨가물, 천연향신료, 양파분말, 고춧가루, 탄산칼슘, 베이킹파우더, 탄산수소나트륨</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>20150471056139</t>
+          <t>2014055607581</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14896,22 +14896,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>20150471056</t>
+          <t>20140556075</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>국산 곤드레</t>
+          <t>사과오리진비니거</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>농업회사법인 한생 주식회사 종천공장</t>
+          <t>농업회사법인 주식회사 초마루</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -14921,7 +14921,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>정제수, 고려엉겅퀴</t>
+          <t>사과, 정제수, 설탕, 효모</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -14980,7 +14980,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>20160345422190</t>
+          <t>20150471056139</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14990,44 +14990,44 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>20160345422</t>
+          <t>20150471056</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>천녹용흑삼환</t>
+          <t>국산 곤드레</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>(주)한제원</t>
+          <t>농업회사법인 한생 주식회사 종천공장</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>인삼발효추출물, 흑삼, 녹용, 침향나무수지가침착된수간목, 참당귀뿌리, 산수유열매, 감초, 황기, 계피가지, 복령균핵, 지황, 작약뿌리, 삽주뿌리줄기, 대추, 천궁뿌리줄기, 사양벌꿀</t>
+          <t>정제수, 고려엉겅퀴</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>20160345422191</t>
+          <t>20160345422190</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>천삼녹용고</t>
+          <t>천녹용흑삼환</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>홍삼, 침향나무수지가침착된수간목, 인삼발효추출물, 녹용, 복령균핵, 생지황즙, 벌꿀</t>
+          <t>인삼발효추출물, 흑삼, 녹용, 침향나무수지가침착된수간목, 참당귀뿌리, 산수유열매, 감초, 황기, 계피가지, 복령균핵, 지황, 작약뿌리, 삽주뿌리줄기, 대추, 천궁뿌리줄기, 사양벌꿀</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -15074,7 +15074,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2016052524456</t>
+          <t>20160345422191</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -15084,44 +15084,44 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>20160525244</t>
+          <t>20160345422</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>맘베베 더 진한 배도라지즙</t>
+          <t>천삼녹용고</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>농업회사법인 유한회사 자연식품</t>
+          <t>(주)한제원</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>배, 도라지, 건조수세미어린열매, 생강, 정제수</t>
+          <t>홍삼, 침향나무수지가침착된수간목, 인삼발효추출물, 녹용, 복령균핵, 생지황즙, 벌꿀</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>20170474063475</t>
+          <t>2016052524456</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -15131,22 +15131,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>20170474063</t>
+          <t>20160525244</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>호박 브이 샷</t>
+          <t>맘베베 더 진한 배도라지즙</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>대원헬스케어주식회사2공장</t>
+          <t>농업회사법인 유한회사 자연식품</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -15156,19 +15156,19 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>서양호박분말, 서양호박농축액, 서양호박농축액, 유산균혼합분말, 당근분말, 팥, 생선콜라겐, 자몽종자추출물, 구연산(무수), 옥수수수염추출분말, Red grape농축액, 늙은호박, 배농축과즙, 호박추출물</t>
+          <t>배, 도라지, 건조수세미어린열매, 생강, 정제수</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>20180456001963</t>
+          <t>20170474063475</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -15178,44 +15178,44 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>20180456001</t>
+          <t>20170474063</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>문경 오미자추출액-KS</t>
+          <t>호박 브이 샷</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>(주)가온에프앤비</t>
+          <t>대원헬스케어주식회사2공장</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>오미자열매, 정제수</t>
+          <t>서양호박분말, 서양호박농축액, 서양호박농축액, 유산균혼합분말, 당근분말, 팥, 생선콜라겐, 자몽종자추출물, 구연산(무수), 옥수수수염추출분말, Red grape농축액, 늙은호박, 배농축과즙, 호박추출물</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>프로바이오틱스</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>20180504025241</t>
+          <t>20180456001963</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -15225,22 +15225,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>20180504025</t>
+          <t>20180456001</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>로열 본(ROYAL BONE)</t>
+          <t>문경 오미자추출액-KS</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>주식회사내츄럴코어</t>
+          <t>(주)가온에프앤비</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -15250,19 +15250,19 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>황산마그네슘, 젖산칼슘, 글루콘산아연, L-아르지닌, 흑마늘농축액, 철갑상어혼합추출액</t>
+          <t>오미자열매, 정제수</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>남성건강</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>201804502622540</t>
+          <t>20180504025241</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -15272,44 +15272,44 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>20180450262</t>
+          <t>20180504025</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>케이엔페퍼</t>
+          <t>로열 본(ROYAL BONE)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>서울향료(주)진천공장</t>
+          <t>주식회사내츄럴코어</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>고춧가루, 복합조미식품, 덱스트린, 향신료올레오레진류</t>
+          <t>황산마그네슘, 젖산칼슘, 글루콘산아연, L-아르지닌, 흑마늘농축액, 철갑상어혼합추출액</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>남성건강</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>20180622215160</t>
+          <t>201804502622540</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>20180622215</t>
+          <t>20180450262</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>용암해수(B)</t>
+          <t>케이엔페퍼</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -15334,17 +15334,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>(재)제주테크노파크용암해수센터</t>
+          <t>서울향료(주)진천공장</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>정제수, 구연산</t>
+          <t>고춧가루, 복합조미식품, 덱스트린, 향신료올레오레진류</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -15356,7 +15356,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>20190456003373</t>
+          <t>20180622215160</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -15366,44 +15366,44 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>20190456003</t>
+          <t>20180622215</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>로얄 프로폴리스 골드</t>
+          <t>용암해수(B)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>농업회사법인주식회사에프앤비바이오</t>
+          <t>(재)제주테크노파크용암해수센터</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>식물혼합추출액, 덱스트린, 말티톨시럽, 사양벌꿀, 배농축액, 생강착즙액, 프로폴리스추출물분말, 동결건조로얄젤리분말, 식물혼합농축액, 기타발효음료, 펙틴, 불로초자실체농축액, 눈꽃동충하초추출분말, 액상차, 홍삼농축액, 민트향, 산화아연, l-멘톨, 건조효모(셀렌함유), 다미아나잎추출분말</t>
+          <t>정제수, 구연산</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>20200385376359</t>
+          <t>20190456003373</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15413,22 +15413,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>20200385376</t>
+          <t>20190456003</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>알룰로스화이트스위트NI</t>
+          <t>로얄 프로폴리스 골드</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>미래식품</t>
+          <t>농업회사법인주식회사에프앤비바이오</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -15438,19 +15438,19 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>향료, 레시틴, 당류가공품, 가공유지, 식물성크림, 혼합분유, 덱스트린, 효소처리스테비아</t>
+          <t>식물혼합추출액, 덱스트린, 말티톨시럽, 사양벌꿀, 배농축액, 생강착즙액, 프로폴리스추출물분말, 동결건조로얄젤리분말, 식물혼합농축액, 기타발효음료, 펙틴, 불로초자실체농축액, 눈꽃동충하초추출분말, 액상차, 홍삼농축액, 민트향, 산화아연, l-멘톨, 건조효모(셀렌함유), 다미아나잎추출분말</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>202102030783661</t>
+          <t>20200385376359</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15460,12 +15460,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>20210203078</t>
+          <t>20200385376</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>베르베린복합분말</t>
+          <t>알룰로스화이트스위트NI</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -15475,29 +15475,29 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>채움바이오 주식회사</t>
+          <t>미래식품</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>과.채가공품, 과.채가공품, 덱스트린, 바나바잎추출물, 기타가공품, 과.채가공품, 효소식품, 비타민B6염산염, 이산화규소, 비타민C, 효모식품, 산화아연, 기타가공품, 기타가공품</t>
+          <t>향료, 레시틴, 당류가공품, 가공유지, 식물성크림, 혼합분유, 덱스트린, 효소처리스테비아</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2021047919776</t>
+          <t>202102030783661</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>20210479197</t>
+          <t>20210203078</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>리제네이드 애프터샷</t>
+          <t>베르베린복합분말</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>(주)피비에이치바이오</t>
+          <t>채움바이오 주식회사</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -15532,19 +15532,19 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>혼합제제, 판토텐산칼슘, 효소처리스테비아, 과.채가공품, 혼합제제, 구연산삼나트륨, 구연산(무수), DL-사과산, 당류가공품, 비타민C, 과.채가공품, 에리스리톨, 글리신, L-글루타민, L-아르지닌, 케르세틴, 산화아연</t>
+          <t>과.채가공품, 과.채가공품, 덱스트린, 바나바잎추출물, 기타가공품, 과.채가공품, 효소식품, 비타민B6염산염, 이산화규소, 비타민C, 효모식품, 산화아연, 기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>20220397234669</t>
+          <t>2021047919776</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15554,12 +15554,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>20220397234</t>
+          <t>20210479197</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>명절 녹두전</t>
+          <t>리제네이드 애프터샷</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -15569,17 +15569,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>㈜슈퍼메이커즈 제2센트럴키친</t>
+          <t>(주)피비에이치바이오</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>콩기름(대두유), 기타가공품</t>
+          <t>혼합제제, 판토텐산칼슘, 효소처리스테비아, 과.채가공품, 혼합제제, 구연산삼나트륨, 구연산(무수), DL-사과산, 당류가공품, 비타민C, 과.채가공품, 에리스리톨, 글리신, L-글루타민, L-아르지닌, 케르세틴, 산화아연</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -15591,7 +15591,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>202202738571306</t>
+          <t>20220397234669</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15601,12 +15601,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>20220273857</t>
+          <t>20220397234</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>발효 서리태 추출분말</t>
+          <t>명절 녹두전</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15616,22 +15616,22 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>(주)네이처코퍼레이션</t>
+          <t>㈜슈퍼메이커즈 제2센트럴키친</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>곡류가공품, 기타가공품, 효모식품, 기타가공품, 덱스트린, 비오틴, 기타가공품, 효소식품, 기타가공품, 비타민C, 이산화규소</t>
+          <t>콩기름(대두유), 기타가공품</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>모발</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -15685,7 +15685,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2022074513726</t>
+          <t>202202738571306</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15695,12 +15695,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>20220745137</t>
+          <t>20220273857</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>고구마볼</t>
+          <t>발효 서리태 추출분말</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15710,29 +15710,29 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>농업회사법인 (주)해남참농가</t>
+          <t>(주)네이처코퍼레이션</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>고구마페이스트, 기타가공품, 곡류가공품</t>
+          <t>곡류가공품, 기타가공품, 효모식품, 기타가공품, 덱스트린, 비오틴, 기타가공품, 효소식품, 기타가공품, 비타민C, 이산화규소</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>모발</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2022074513727</t>
+          <t>2022074513726</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>고구마치즈볼</t>
+          <t>고구마볼</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>고구마페이스트, 기타가공품, 치즈, 소스, 곡류가공품</t>
+          <t>고구마페이스트, 기타가공품, 곡류가공품</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15779,7 +15779,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>20230528144350</t>
+          <t>2022074513727</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20220745137</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>300달톤 저분자 어린 피쉬콜라겐 엘라스틴</t>
+          <t>고구마치즈볼</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>농업회사법인 (주)해남참농가</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -15814,19 +15814,19 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>이산화규소, 유청칼슘, 식품첨가물혼합제제, 엘라스틴가수분해물, 식물성크림, 당류가공품, 기타가공품, 에리스리톨, 비타민C, 포도당, 생선콜라겐분말, 히알루론산혼합제제, 합성향료, 혼합분유</t>
+          <t>고구마페이스트, 기타가공품, 치즈, 소스, 곡류가공품</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>20230517987173</t>
+          <t>20230528144350</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15836,12 +15836,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>20230517987</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>아세로라 밸런스 포뮬러</t>
+          <t>300달톤 저분자 어린 피쉬콜라겐 엘라스틴</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -15851,29 +15851,29 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>(주)디에스푸드웰 화성지점</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>과.채가공품, 과.채가공품, 결정셀룰로스, 비타민C, D-소비톨, L-테아닌(고시형), 타우린, 기타가공품, 산화아연, 바나바잎 추출물(고시형), 스테아린산</t>
+          <t>이산화규소, 유청칼슘, 식품첨가물혼합제제, 엘라스틴가수분해물, 식물성크림, 당류가공품, 기타가공품, 에리스리톨, 비타민C, 포도당, 생선콜라겐분말, 히알루론산혼합제제, 합성향료, 혼합분유</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>20230517987174</t>
+          <t>20230517987173</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>그린 아세로라 빌베리C</t>
+          <t>아세로라 밸런스 포뮬러</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>기타가공품, 이산화규소, 스테아린산마그네슘</t>
+          <t>과.채가공품, 과.채가공품, 결정셀룰로스, 비타민C, D-소비톨, L-테아닌(고시형), 타우린, 기타가공품, 산화아연, 바나바잎 추출물(고시형), 스테아린산</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15920,7 +15920,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>20230609874602</t>
+          <t>20230517987174</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15930,22 +15930,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>20230609874</t>
+          <t>20230517987</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 버닝</t>
+          <t>그린 아세로라 빌베리C</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>(주)뉴트리션바이오</t>
+          <t>(주)디에스푸드웰 화성지점</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -15955,19 +15955,19 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>기타가공품, 기타가공품, 난소화성말토덱스트린(고시형), 기타가공품, 과.채가공품, 기타 농산가공품, 이산화규소, 스테아린산마그네슘, 식품첨가물</t>
+          <t>기타가공품, 이산화규소, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025085404716</t>
+          <t>20230609874602</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15977,22 +15977,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>20250854047</t>
+          <t>20230609874</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>프레쉬벨 사과당근</t>
+          <t>파라다이스 그레인 버닝</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>농업회사법인 주식회사 프레쉬벨</t>
+          <t>(주)뉴트리션바이오</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>비타민C, 당근, 사과</t>
+          <t>기타가공품, 기타가공품, 난소화성말토덱스트린(고시형), 기타가공품, 과.채가공품, 기타 농산가공품, 이산화규소, 스테아린산마그네슘, 식품첨가물</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -16014,7 +16014,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>20250470999171</t>
+          <t>2025085404716</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16024,44 +16024,44 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>20250470999</t>
+          <t>20250854047</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>파로로효소</t>
+          <t>프레쉬벨 사과당근</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>효소식품</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>주식회사 비에스바이오</t>
+          <t>농업회사법인 주식회사 프레쉬벨</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>당류가공품, 효소식품, 포도당, 덱스트린, 효소식품, 대나무수액, 향료, 매실추출분말, 대추추출농축액분말, 아티초크분말, 효소식품, 이산화규소, 혼합제제, 기타가공품, 효소식품, 기타가공품</t>
+          <t>비타민C, 당근, 사과</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>효소</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>20260559122163</t>
+          <t>20250470999171</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16071,22 +16071,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>20260559122</t>
+          <t>20250470999</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 오리지널</t>
+          <t>파로로효소</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>효소식품</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>(주)코스모바이오</t>
+          <t>주식회사 비에스바이오</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -16096,12 +16096,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>기타 농산가공품, 기타가공품, 과.채가공품, 기타가공품, 기타가공품, 고형차, 과.채가공품, 스테아린산마그네슘, 이산화규소, 효소식품, 과.채가공품, 기타가공품</t>
+          <t>당류가공품, 효소식품, 포도당, 덱스트린, 효소식품, 대나무수액, 향료, 매실추출분말, 대추추출농축액분말, 아티초크분말, 효소식품, 이산화규소, 혼합제제, 기타가공품, 효소식품, 기타가공품</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -16155,7 +16155,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>20260559122158</t>
+          <t>20260559122166</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16170,12 +16170,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>식물성 멜라토닌 함유 멜라다임 포레스트</t>
+          <t>파라다이스 그레인 퍼플</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -16185,24 +16185,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>기타가공품, 과.채가공품, 과.채가공품, 기타가공품, L-트립토판, 기타가공품, 테아닌, 비타민C, 비타민B6염산염, 혼합제제, 이산화규소, 스테아린산마그네슘, 산화마그네슘, 엽산, 유단백가수분해물</t>
+          <t>락토페린농축물, 스테아린산마그네슘, 유함유가공품, 기타가공품, 효소식품, 기타가공품</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>20260559122167</t>
+          <t>20260559122158</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16217,12 +16217,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 이너 밸런스</t>
+          <t>식물성 멜라토닌 함유 멜라다임 포레스트</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -16232,24 +16232,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>기타가공품, 이산화규소, 스테아린산마그네슘</t>
+          <t>기타가공품, 과.채가공품, 과.채가공품, 기타가공품, L-트립토판, 기타가공품, 테아닌, 비타민C, 비타민B6염산염, 혼합제제, 이산화규소, 스테아린산마그네슘, 산화마그네슘, 엽산, 유단백가수분해물</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>20260559122166</t>
+          <t>20260559122163</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 퍼플</t>
+          <t>파라다이스 그레인 오리지널</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>락토페린농축물, 스테아린산마그네슘, 유함유가공품, 기타가공품, 효소식품, 기타가공품</t>
+          <t>기타 농산가공품, 기타가공품, 과.채가공품, 기타가공품, 기타가공품, 고형차, 과.채가공품, 스테아린산마그네슘, 이산화규소, 효소식품, 과.채가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -16296,42 +16296,42 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1996037801360</t>
+          <t>20260559122167</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>19960378013</t>
+          <t>20260559122</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>네니아 착즙 사과당근배주스</t>
+          <t>파라다이스 그레인 이너 밸런스</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>농업회사법인미디안농산주식회사</t>
+          <t>(주)코스모바이오</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>당근, 배, 사과</t>
+          <t>기타가공품, 이산화규소, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -16343,7 +16343,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>20170614111866</t>
+          <t>1996037801360</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16353,44 +16353,44 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>20170614111</t>
+          <t>19960378013</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>유기농 레드와인비니거 알파 스틱</t>
+          <t>네니아 착즙 사과당근배주스</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>(주)엔트리</t>
+          <t>농업회사법인미디안농산주식회사</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>당근, 배, 사과</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>20190473163266</t>
+          <t>20080464214795</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16400,44 +16400,44 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>20190473163</t>
+          <t>20080464214</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>사증사포 홍도라지농축액</t>
+          <t>유자분말SG-5786</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>농업회사법인(주)글로벌금산진생</t>
+          <t>주식회사 세계에프엘</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>도라지뿌리농축액</t>
+          <t>정제수, 유자, 유자과즙, 물엿</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>20210391247112</t>
+          <t>20170614111866</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16447,44 +16447,44 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>20210391247</t>
+          <t>20170614111</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>소다향시럽</t>
+          <t>유기농 레드와인비니거 알파 스틱</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>이안스코리아(주)</t>
+          <t>(주)엔트리</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>식용색소청색제1호, 수크랄로스, 소브산칼륨, 구연산삼나트륨, DL-사과산, 구연산(무수), 소다향, 액상과당, 백설탕, 정제수</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>20210391247111</t>
+          <t>20190473163266</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16494,44 +16494,44 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>20210391247</t>
+          <t>20190473163</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>체리향시럽</t>
+          <t>사증사포 홍도라지농축액</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>이안스코리아(주)</t>
+          <t>농업회사법인(주)글로벌금산진생</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>식용색소적색제102호, 수크랄로스, 구연산삼나트륨, 카라멜색소 Ⅳ, 소브산칼륨, 체리향, 구연산(무수), 액상과당, 정제수, 백설탕</t>
+          <t>도라지뿌리농축액</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>20210036719245</t>
+          <t>20210391247111</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16541,44 +16541,44 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>20210036719</t>
+          <t>20210391247</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>블루베리농축분말</t>
+          <t>체리향시럽</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>(주)비에스에프코리아</t>
+          <t>이안스코리아(주)</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>블루베리농축분말, 기타가공품</t>
+          <t>식용색소적색제102호, 수크랄로스, 구연산삼나트륨, 카라멜색소 Ⅳ, 소브산칼륨, 체리향, 구연산(무수), 액상과당, 정제수, 백설탕</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>20230528144358</t>
+          <t>20210391247112</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16588,44 +16588,44 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20210391247</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>제주산 청정여주 발효효소</t>
+          <t>소다향시럽</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>효소식품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>이안스코리아(주)</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>여주추출분말, 효소식품, 이소말트, 효소식품, 효소처리스테비아, 이산화규소, 합성향료, 당류가공품, 효소식품, 곡류가공품, 분리대두단백</t>
+          <t>식용색소청색제1호, 수크랄로스, 소브산칼륨, 구연산삼나트륨, DL-사과산, 구연산(무수), 소다향, 액상과당, 백설탕, 정제수</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>효소</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>20230528144353</t>
+          <t>20210036719245</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16635,12 +16635,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20210036719</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>지중해 클렌즈</t>
+          <t>블루베리농축분말</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -16650,67 +16650,161 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>(주)비에스에프코리아</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260905</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>자일리톨, 구연산(무수), 덱스트린, 과.채가공품, 효소처리스테비아, 레몬향분말, 벌꿀분말, 오렌지추출물분말, DL-사과산, 이산화규소, 오렌지향코톤, 식물혼합추출농축분말, 파슬리분말, 재제소금(재제조소금), 아미노산혼합제제, 수크랄로스, 녹차추출물분말가루, 타우린</t>
+          <t>블루베리농축분말, 기타가공품</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>피로개선</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
+          <t>20230528144358</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>20260904</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>20230528144</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>제주산 청정여주 발효효소</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>효소식품</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>바이오디피씨(주)</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>여주추출분말, 효소식품, 이소말트, 효소식품, 효소처리스테비아, 이산화규소, 합성향료, 당류가공품, 효소식품, 곡류가공품, 분리대두단백</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>효소</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>20230528144353</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>20260904</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>20230528144</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>지중해 클렌즈</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>바이오디피씨(주)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>자일리톨, 구연산(무수), 덱스트린, 과.채가공품, 효소처리스테비아, 레몬향분말, 벌꿀분말, 오렌지추출물분말, DL-사과산, 이산화규소, 오렌지향코톤, 식물혼합추출농축분말, 파슬리분말, 재제소금(재제조소금), 아미노산혼합제제, 수크랄로스, 녹차추출물분말가루, 타우린</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>피로개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
           <t>20260559122175</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>20260904</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>20260559122</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D195" t="inlineStr">
         <is>
           <t>리셀바인</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E195" t="inlineStr">
         <is>
           <t>고형차</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>(주)코스모바이오</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>20260904</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
         <is>
           <t>기타가공품, 비타민B6염산염, 기타가공품, 결정셀룰로스, 판토텐산칼슘, 스테아린산마그네슘, 이산화규소, 산화아연, 니코틴산아미드</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
+      <c r="I195" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
@@ -19807,7 +19901,7 @@
         <v>6</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L45" s="10" t="n">
         <v>3</v>
@@ -19831,10 +19925,10 @@
         <v>13</v>
       </c>
       <c r="S45" s="10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T45" s="8" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46">
@@ -19871,7 +19965,7 @@
         <v>-27</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>-16</v>
@@ -19895,10 +19989,10 @@
         <v>-66</v>
       </c>
       <c r="S46" s="12" t="n">
-        <v>-1026</v>
+        <v>-1025</v>
       </c>
       <c r="T46" s="12" t="n">
-        <v>-1732</v>
+        <v>-1730</v>
       </c>
     </row>
     <row r="47">
@@ -19999,7 +20093,7 @@
         <v>-6</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>-3</v>
@@ -20023,10 +20117,10 @@
         <v>-13</v>
       </c>
       <c r="S48" s="12" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="T48" s="12" t="n">
-        <v>-192</v>
+        <v>-194</v>
       </c>
     </row>
     <row r="49">

--- a/output/2026-09_품목신고보고현황.xlsx
+++ b/output/2026-09_품목신고보고현황.xlsx
@@ -12194,7 +12194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I619"/>
+  <dimension ref="A1:I634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15031,7 +15031,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>202102030783658</t>
+          <t>202102030783656</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15046,12 +15046,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>리포좀NMN 99</t>
+          <t>루비베린</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -15061,17 +15061,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>스테아린산마그네슘, 기타가공품</t>
+          <t>과.채가공품, 덱스트린, 결정셀룰로스, 과.채가공품, 기타가공품, 혼합제제, 이산화규소, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -15125,7 +15125,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>202102030783656</t>
+          <t>202102030783655</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>루비베린</t>
+          <t>에버케어 구강유래유산균</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -15160,19 +15160,19 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>과.채가공품, 덱스트린, 결정셀룰로스, 과.채가공품, 기타가공품, 혼합제제, 이산화규소, 스테아린산마그네슘</t>
+          <t>D-소비톨, 자일리톨, 프락토올리고당(고시형), 기타가공품, 혼합제제, 기타가공품, 이산화규소, 스테아린산마그네슘, 스테비텐후레쉬, 프로바이오틱스(고시형), 프로폴리스추출물분말, 식품첨가물혼합제제, 산화아연</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>202102030783655</t>
+          <t>202102030783658</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -15187,12 +15187,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>에버케어 구강유래유산균</t>
+          <t>리포좀NMN 99</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15202,17 +15202,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>D-소비톨, 자일리톨, 프락토올리고당(고시형), 기타가공품, 혼합제제, 기타가공품, 이산화규소, 스테아린산마그네슘, 스테비텐후레쉬, 프로바이오틱스(고시형), 프로폴리스추출물분말, 식품첨가물혼합제제, 산화아연</t>
+          <t>스테아린산마그네슘, 기타가공품</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -18227,7 +18227,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>202102030783660</t>
+          <t>202102030783659</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -18242,12 +18242,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>그린 아세로라 99</t>
+          <t>그린 아세로라 추출물</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18257,12 +18257,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>스테아린산마그네슘, 기타가공품</t>
+          <t>이산화규소, 난소화성말토덱스트린(고시형), 과.채가공품, 과.채가공품, 비타민C, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -18274,7 +18274,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>202102030783659</t>
+          <t>202102030783662</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>그린 아세로라 추출물</t>
+          <t>미람유 베르베린 시그니처 99</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18304,24 +18304,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>이산화규소, 난소화성말토덱스트린(고시형), 과.채가공품, 과.채가공품, 비타민C, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품</t>
+          <t>스테아린산마그네슘, 기타가공품</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>202102030783662</t>
+          <t>202102030783660</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>미람유 베르베린 시그니처 99</t>
+          <t>그린 아세로라 99</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
@@ -18445,7 +18445,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -24696,7 +24696,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -25965,7 +25965,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -26012,7 +26012,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -27093,7 +27093,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -28268,7 +28268,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -28315,7 +28315,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -31417,7 +31417,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -32075,7 +32075,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>202206834731771</t>
+          <t>202206834731689</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -32107,7 +32107,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>젖산마그네슘 컴플렉스</t>
+          <t>솔리오노 필</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -32122,12 +32122,12 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>이눌린/치커리추출물(고시형), 당류가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
+          <t>식품첨가물, 식품첨가물, 식품첨가물, 고형차</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -32139,7 +32139,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>202206834731776</t>
+          <t>202206834731684</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -32154,12 +32154,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>트리뷸러스+알파</t>
+          <t>청명본서 청명진</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -32174,7 +32174,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>고형차, 기타가공품, 기타가공품, 식품첨가물, 덱스트린, 이눌린/치커리추출물(고시형), 과.채가공품, 식품첨가물, 식품첨가물, 식품첨가물, 효모식품, 과.채가공품, 과.채가공품</t>
+          <t>포도당, 기타가공품, 기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -32186,7 +32186,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>202206834731684</t>
+          <t>202206834731778</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -32201,12 +32201,12 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>청명본서 청명진</t>
+          <t>야관문루버스복분자혼합분말</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -32216,12 +32216,12 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>포도당, 기타가공품, 기타가공품, 기타가공품</t>
+          <t>기타가공품, 식품첨가물, 과.채가공품, 식품첨가물, 덱스트린, 기타가공품, 이눌린/치커리추출물(고시형)</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -32233,7 +32233,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>202206834731696</t>
+          <t>202206834731774</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -32248,7 +32248,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>마가비책 마가목 추출물</t>
+          <t>삼백초 추출물 복합물</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -32263,12 +32263,12 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>식품첨가물, 고형차</t>
+          <t>과.채가공품, 과.채가공품, 기타가공품, 식품첨가물, 포도당, 기타가공품</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -32280,7 +32280,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>202206834731689</t>
+          <t>202206834731776</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -32295,7 +32295,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>솔리오노 필</t>
+          <t>트리뷸러스+알파</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -32310,12 +32310,12 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>식품첨가물, 식품첨가물, 식품첨가물, 고형차</t>
+          <t>고형차, 기타가공품, 기타가공품, 식품첨가물, 덱스트린, 이눌린/치커리추출물(고시형), 과.채가공품, 식품첨가물, 식품첨가물, 식품첨가물, 효모식품, 과.채가공품, 과.채가공품</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -32357,7 +32357,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -32374,7 +32374,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>202206834731774</t>
+          <t>202206834731771</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -32389,7 +32389,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>삼백초 추출물 복합물</t>
+          <t>젖산마그네슘 컴플렉스</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -32404,12 +32404,12 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>과.채가공품, 과.채가공품, 기타가공품, 식품첨가물, 포도당, 기타가공품</t>
+          <t>이눌린/치커리추출물(고시형), 당류가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -32421,7 +32421,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>202206834731778</t>
+          <t>202206834731691</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>야관문루버스복분자혼합분말</t>
+          <t>영양바른 서리태 비오틴 맥스 10000</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -32451,17 +32451,17 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>기타가공품, 식품첨가물, 과.채가공품, 식품첨가물, 덱스트린, 기타가공품, 이눌린/치커리추출물(고시형)</t>
+          <t>식품첨가물, 고형차</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>모발</t>
         </is>
       </c>
     </row>
@@ -32498,7 +32498,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -32515,7 +32515,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>202206834731691</t>
+          <t>202206834731696</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -32530,7 +32530,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>영양바른 서리태 비오틴 맥스 10000</t>
+          <t>마가비책 마가목 추출물</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -32545,7 +32545,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -32555,7 +32555,7 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>모발</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -33109,7 +33109,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -34613,7 +34613,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -35523,7 +35523,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>202206834731780</t>
+          <t>202206834731782</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -35538,7 +35538,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>젖산마그네슘분말복합물</t>
+          <t>레드와인비니거 레드포뮬라</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -35553,24 +35553,24 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 덱스트린, 당류가공품, 식품첨가물, 이눌린/치커리추출물(고시형)</t>
+          <t>기타가공품, 바나바잎 추출물(고시형), 기타가공품, 식품첨가물혼합제제, 식품첨가물, 기타가공품, 기타가공품, 음료베이스, 기타가공품, 식품첨가물, 과.채가공품, 식품첨가물, 덱스트린, 올리고당, 이눌린/치커리추출물(고시형)</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>20220495001369</t>
+          <t>202206834731784</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -35580,44 +35580,44 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>20220495001</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>그린몬스터 디톡 콤부차 허니자몽</t>
+          <t>팜데이 폴리코사놀 복합물</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>(주)한미양행 선유공장</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>수크랄로스, 과.채가공품, 고형차, 기타가공품, 당류가공품, 효소처리스테비아, 향료, 당류가공품, 프로바이오틱스(고시형), 구연산(무수), 탄산수소나트륨, 에리스리톨, 고형차</t>
+          <t>식품첨가물, 기타가공품, 기타가공품, 식품첨가물, 식품첨가물, 귀리식이섬유(고시형), 이눌린/치커리추출물(고시형), 식품첨가물, 기타가공품, 올리고당, 덱스트린, 식품첨가물</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>20220495001367</t>
+          <t>202206834731780</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -35627,12 +35627,12 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>20220495001</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>그린몬스터 디톡 콤부차</t>
+          <t>젖산마그네슘분말복합물</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -35642,29 +35642,29 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>(주)한미양행 선유공장</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>수크랄로스, 당류가공품, 고형차, 당류가공품, 향료, 효소처리스테비아, 과.채가공품, 이산화규소, 프로바이오틱스(고시형), 구연산(무수), 탄산수소나트륨, 에리스리톨, 고형차, 과.채가공품</t>
+          <t>식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 덱스트린, 당류가공품, 식품첨가물, 이눌린/치커리추출물(고시형)</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>20220495001368</t>
+          <t>202206834731786</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -35674,12 +35674,12 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>20220495001</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>그린몬스터 디톡 콤부차 석류 히비스커스</t>
+          <t>식물성 복합물 CBM-6</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -35689,29 +35689,29 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>(주)한미양행 선유공장</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>당류가공품, 과.채가공품, 고형차, 에리스리톨, 탄산수소나트륨, 구연산(무수), 혼합제제, 고형차, 당류가공품, 기타 농산가공품, 효소처리스테비아, 과.채가공품, 이산화규소, 과.채가공품, 프로바이오틱스(고시형), 수크랄로스</t>
+          <t>기타가공품, 기타가공품, 이눌린/치커리추출물(고시형), 기타가공품, 기타가공품, 과.채가공품</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>20220495001370</t>
+          <t>202206834731725</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -35721,44 +35721,44 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>20220495001</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>그린몬스터 디톡 콤부차 패션후르츠</t>
+          <t>유단백 MBP 포뮬러</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>(주)한미양행 선유공장</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>수크랄로스, 프로바이오틱스(고시형), 구연산(무수), 탄산수소나트륨, 에리스리톨, 고형차, 과.채가공품, 당류가공품, 고형차, 혼합제제, 당류가공품, 효소처리스테비아, 과.채가공품, 이산화규소</t>
+          <t>유함유가공품, 기타 농산가공품, 유함유가공품, 식품첨가물, 유청단백분말, 유청단백분말, 두류가공품, 식품첨가물, 올리고당, 포도당, 기타 수산물가공품, 고형차</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>20230612332342</t>
+          <t>202206834731700</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -35768,44 +35768,44 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>20230612332</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>제주산 당당한 여주 발효효소</t>
+          <t>서리모아 서리태 맥주효모</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>효소식품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>(주)웰레스트</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>뚱딴지추출분말, 양배추분말, 바나바잎분말, 곡류가공품, 이산화규소, 난소화성말토덱스트린(고시형), 효소식품, 볶은콩가루, 분리대두단백, 곡류가공품, 효소식품, 기타가공품</t>
+          <t>식품첨가물, 고형차</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>효소</t>
+          <t>모발</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>20230609874606</t>
+          <t>202206834731781</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -35815,32 +35815,32 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>20230609874</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>키오스 매스틱 플러스</t>
+          <t>데이셋 젖산마그네슘 코어</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>(주)뉴트리션바이오</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>식품첨가물, 기타 농산가공품, 기타가공품, 이산화규소, 기타가공품, 기타가공품, 과.채가공품, 과.채가공품, 포도당, 올리고당, 기타가공품, 난소화성말토덱스트린(고시형)</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -35852,7 +35852,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>202409550425</t>
+          <t>202206834731702</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -35862,32 +35862,32 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>20240955042</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>두나골드 화이버(DUNAGOLD FIBER)</t>
+          <t>맥앤톡</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>(주)케이마린바이오테크</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>구연산, 난소화성말토덱스트린분말(고시형), 기타가공품</t>
+          <t>식품첨가물, 고형차</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -35899,7 +35899,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>20240658113239</t>
+          <t>20220495001369</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -35909,32 +35909,32 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>20240658113</t>
+          <t>20220495001</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>토종유산균 SPC-SNU (L. sanfranciscensis)</t>
+          <t>그린몬스터 디톡 콤부차 허니자몽</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>(주)메디오젠</t>
+          <t>(주)한미양행 선유공장</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Fructilactobacillus sanfranciscensis, 덱스트린</t>
+          <t>수크랄로스, 과.채가공품, 고형차, 기타가공품, 당류가공품, 효소처리스테비아, 향료, 당류가공품, 프로바이오틱스(고시형), 구연산(무수), 탄산수소나트륨, 에리스리톨, 고형차</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -35946,7 +35946,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>20240203422237</t>
+          <t>20220495001367</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -35956,44 +35956,44 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>20240203422</t>
+          <t>20220495001</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>마가목혼합추출액</t>
+          <t>그린몬스터 디톡 콤부차</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>주식회사 미쁨생활건강</t>
+          <t>(주)한미양행 선유공장</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>마가목, 마가목열매, 배추출액, 도라지뿌리, 참당귀, 정제수, 은행나무잎, 지황, 천궁뿌리줄기, 황기, 계피, 감초, 작약뿌리</t>
+          <t>수크랄로스, 당류가공품, 고형차, 당류가공품, 향료, 효소처리스테비아, 과.채가공품, 이산화규소, 프로바이오틱스(고시형), 구연산(무수), 탄산수소나트륨, 에리스리톨, 고형차, 과.채가공품</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>20240203422240</t>
+          <t>20220495001368</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -36003,44 +36003,44 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>20240203422</t>
+          <t>20220495001</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>딱좋아석류콜라겐스틱</t>
+          <t>그린몬스터 디톡 콤부차 석류 히비스커스</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>주식회사 미쁨생활건강</t>
+          <t>(주)한미양행 선유공장</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>구연산, 혼합제제, 기타가공품, 석류농축액</t>
+          <t>당류가공품, 과.채가공품, 고형차, 에리스리톨, 탄산수소나트륨, 구연산(무수), 혼합제제, 고형차, 당류가공품, 기타 농산가공품, 효소처리스테비아, 과.채가공품, 이산화규소, 과.채가공품, 프로바이오틱스(고시형), 수크랄로스</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>20240203422238</t>
+          <t>20220495001370</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -36050,44 +36050,44 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>20240203422</t>
+          <t>20220495001</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>마가활력보</t>
+          <t>그린몬스터 디톡 콤부차 패션후르츠</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>주식회사 미쁨생활건강</t>
+          <t>(주)한미양행 선유공장</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>자몽종자추출물, 쇠무릅뿌리추출분말, 소연골추출분말, 당류가공품, 혼합제제, 액상차</t>
+          <t>수크랄로스, 프로바이오틱스(고시형), 구연산(무수), 탄산수소나트륨, 에리스리톨, 고형차, 과.채가공품, 당류가공품, 고형차, 혼합제제, 당류가공품, 효소처리스테비아, 과.채가공품, 이산화규소</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>20240203422239</t>
+          <t>20230612332342</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -36097,44 +36097,44 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>20240203422</t>
+          <t>20230612332</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>블루베리콜라겐젤리스틱</t>
+          <t>제주산 당당한 여주 발효효소</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>효소식품</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>주식회사 미쁨생활건강</t>
+          <t>(주)웰레스트</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>블루베리농축액, 생선콜라겐펩타이드분말, 혼합제제, 산도조절제</t>
+          <t>뚱딴지추출분말, 양배추분말, 바나바잎분말, 곡류가공품, 이산화규소, 난소화성말토덱스트린(고시형), 효소식품, 볶은콩가루, 분리대두단백, 곡류가공품, 효소식품, 기타가공품</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2024071214433</t>
+          <t>20230609874606</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -36144,12 +36144,12 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>20240712144</t>
+          <t>20230609874</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>차조기추출(농축)분말</t>
+          <t>키오스 매스틱 플러스</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -36159,17 +36159,17 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>(주)신우코퍼레이션</t>
+          <t>(주)뉴트리션바이오</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>덱스트린, 기타가공품</t>
+          <t>식품첨가물, 기타 농산가공품, 기타가공품, 이산화규소, 기타가공품, 기타가공품, 과.채가공품, 과.채가공품, 포도당, 올리고당, 기타가공품, 난소화성말토덱스트린(고시형)</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -36181,7 +36181,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2024011872847</t>
+          <t>202409550425</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -36191,32 +36191,32 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>20240118728</t>
+          <t>20240955042</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>셀렉커피랩 빙수밀크파우더</t>
+          <t>두나골드 화이버(DUNAGOLD FIBER)</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>바모스에프앤비</t>
+          <t>(주)케이마린바이오테크</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>백설탕, 결정과당, 식물성크림, 혼합분유, 유청분말, 향료, 수크랄로스</t>
+          <t>구연산, 난소화성말토덱스트린분말(고시형), 기타가공품</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -36228,7 +36228,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2024011872848</t>
+          <t>20240658113239</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -36238,22 +36238,22 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>20240118728</t>
+          <t>20240658113</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>셀렉커피랩 말차파우더</t>
+          <t>토종유산균 SPC-SNU (L. sanfranciscensis)</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>바모스에프앤비</t>
+          <t>(주)메디오젠</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -36263,19 +36263,19 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>덱스트린, 백설탕, 녹차가루</t>
+          <t>Fructilactobacillus sanfranciscensis, 덱스트린</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>202509370124</t>
+          <t>20240203422237</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -36285,22 +36285,22 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>20250937012</t>
+          <t>20240203422</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>샤인머스켓주스</t>
+          <t>마가목혼합추출액</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>창녕다움가공센터</t>
+          <t>주식회사 미쁨생활건강</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
@@ -36310,19 +36310,19 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>DL-사과산, L-주석산, 향료, 비타민C, 포도과육</t>
+          <t>마가목, 마가목열매, 배추출액, 도라지뿌리, 참당귀, 정제수, 은행나무잎, 지황, 천궁뿌리줄기, 황기, 계피, 감초, 작약뿌리</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2025020332634</t>
+          <t>20240203422240</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -36332,22 +36332,22 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>20250203326</t>
+          <t>20240203422</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>NFC 100% 갈아만든 블루베리즙</t>
+          <t>딱좋아석류콜라겐스틱</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>청담푸드</t>
+          <t>주식회사 미쁨생활건강</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
@@ -36357,19 +36357,19 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>블루베리착즙액</t>
+          <t>구연산, 혼합제제, 기타가공품, 석류농축액</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>202507833198</t>
+          <t>20240203422238</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -36379,22 +36379,22 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>20250783319</t>
+          <t>20240203422</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>수제 동그랑땡</t>
+          <t>마가활력보</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>농업회사법인 바잘농산물 주식회사</t>
+          <t>주식회사 미쁨생활건강</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -36404,19 +36404,19 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>후추가루, 참기름, 정제소금, 백설탕, 콩기름(대두유), 마늘, 두부, 돼지고기, 밀가루, 대파, 당근, 양파, 계란</t>
+          <t>자몽종자추출물, 쇠무릅뿌리추출분말, 소연골추출분말, 당류가공품, 혼합제제, 액상차</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2025078331911</t>
+          <t>20240203422239</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -36426,44 +36426,44 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>20250783319</t>
+          <t>20240203422</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>수제 녹두전</t>
+          <t>블루베리콜라겐젤리스틱</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>농업회사법인 바잘농산물 주식회사</t>
+          <t>주식회사 미쁨생활건강</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>혼합식용유, 팽이버섯, 숙주나물, 돼지고기, 깐녹두, 정제수, 멸치액, 마늘, 정제소금, 멥쌀, 찹쌀, 설탕, 후추가루, 생강</t>
+          <t>블루베리농축액, 생선콜라겐펩타이드분말, 혼합제제, 산도조절제</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>202507833197</t>
+          <t>2024071214433</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -36473,12 +36473,12 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>20250783319</t>
+          <t>20240712144</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>수제 동태전</t>
+          <t>차조기추출(농축)분말</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -36488,7 +36488,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>농업회사법인 바잘농산물 주식회사</t>
+          <t>(주)신우코퍼레이션</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -36498,7 +36498,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>후추가루, 마늘, 정제소금, 콩기름(대두유), 정제수, 밀가루, 계란, 황태포</t>
+          <t>덱스트린, 기타가공품</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -36510,7 +36510,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>202604216591</t>
+          <t>2024011872847</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -36520,22 +36520,22 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>20260421659</t>
+          <t>20240118728</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>캔디유 러브믹스 수제사탕</t>
+          <t>셀렉커피랩 빙수밀크파우더</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>캔디유</t>
+          <t>바모스에프앤비</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -36545,7 +36545,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>치자청색소, 오징어먹물색소, 락색소, 블루베리향, 라즈베리향, 복숭아향, 패션후르츠향, 딸기향, 이산화티타늄, 구연산, 프락토올리고당, 백설탕, 식품첨가물혼합제제</t>
+          <t>백설탕, 결정과당, 식물성크림, 혼합분유, 유청분말, 향료, 수크랄로스</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -36557,7 +36557,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>202604216594</t>
+          <t>2024011872848</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -36567,32 +36567,32 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>20260421659</t>
+          <t>20240118728</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>캔디유 합격캔디 수제사탕</t>
+          <t>셀렉커피랩 말차파우더</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>캔디유</t>
+          <t>바모스에프앤비</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>백설탕, 프락토올리고당, 구연산, 이산화티타늄, 레몬향, 오징어먹물색소, 딸기향, 패션후르츠향, 복숭아향, 라임향, 치자황색소, 혼합제제, 치자청색소, 락색소</t>
+          <t>덱스트린, 백설탕, 녹차가루</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -36604,7 +36604,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>202604216593</t>
+          <t>202509370124</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -36614,32 +36614,32 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>20260421659</t>
+          <t>20250937012</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>캔디유 플라워믹스 수제사탕</t>
+          <t>샤인머스켓주스</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>캔디유</t>
+          <t>창녕다움가공센터</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>요거트향, 치자황색소, 치자황색소, 포도향, 요구르트향, 블루베리향, 이산화티타늄, 구연산, 프락토올리고당, 백설탕, 라임향, 딸기향, 레몬향, 혼합제제, 락색소</t>
+          <t>DL-사과산, L-주석산, 향료, 비타민C, 포도과육</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -36651,7 +36651,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>202604216595</t>
+          <t>2025020332634</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -36661,44 +36661,44 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>20260421659</t>
+          <t>20250203326</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>캔디유 후르츠믹스 수제사탕</t>
+          <t>NFC 100% 갈아만든 블루베리즙</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>캔디유</t>
+          <t>청담푸드</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>백설탕, 프락토올리고당, 구연산, 이산화티타늄, 치자황색소, 딸기향, 감귤향, 레몬향, 라임향, 복숭아향, 락색소, 치자청색소, 혼합제제</t>
+          <t>블루베리착즙액</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>202604216592</t>
+          <t>202507833198</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -36708,22 +36708,22 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>20260421659</t>
+          <t>20250783319</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>캔디유 사우어믹스 수제사탕</t>
+          <t>수제 동그랑땡</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>캔디유</t>
+          <t>농업회사법인 바잘농산물 주식회사</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -36733,7 +36733,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>락색소, 치자청색소, 감귤향, 라임향, 레몬향, 치자황색소, 이산화티타늄, 비타민C, 구연산, 프락토올리고당, 백설탕</t>
+          <t>후추가루, 참기름, 정제소금, 백설탕, 콩기름(대두유), 마늘, 두부, 돼지고기, 밀가루, 대파, 당근, 양파, 계란</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -36745,7 +36745,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>20260559122192</t>
+          <t>2025078331911</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -36755,44 +36755,44 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>20260559122</t>
+          <t>20250783319</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>수용성 커큐민 바이오페린</t>
+          <t>수제 녹두전</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>(주)코스모바이오</t>
+          <t>농업회사법인 바잘농산물 주식회사</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>기타 농산가공품, 결정셀룰로스, 옥수수전분, 기타가공품, 고형차, 기타가공품, 과.채가공품, 비타민C, 이산화규소, 스테아린산마그네슘, 기타 농산가공품</t>
+          <t>혼합식용유, 팽이버섯, 숙주나물, 돼지고기, 깐녹두, 정제수, 멸치액, 마늘, 정제소금, 멥쌀, 찹쌀, 설탕, 후추가루, 생강</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>20260559122194</t>
+          <t>202507833197</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -36802,22 +36802,22 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>20260559122</t>
+          <t>20250783319</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>서리올맥스</t>
+          <t>수제 동태전</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>(주)코스모바이오</t>
+          <t>농업회사법인 바잘농산물 주식회사</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -36827,7 +36827,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>기타가공품, 스테아린산마그네슘</t>
+          <t>후추가루, 마늘, 정제소금, 콩기름(대두유), 정제수, 밀가루, 계란, 황태포</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -36839,7 +36839,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>20260559122191</t>
+          <t>202604216591</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -36849,22 +36849,22 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>20260559122</t>
+          <t>20260421659</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>리체르카 식물성 멜라토닌 함유 2mg</t>
+          <t>캔디유 러브믹스 수제사탕</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>(주)코스모바이오</t>
+          <t>캔디유</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -36874,19 +36874,19 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>기타 농산가공품, 과.채가공품, 기타가공품, 기타가공품, 고형차, 기타가공품, L-트립토판, 테아닌, 기타가공품, 가바, 혼합제제, 스테아린산마그네슘, 산화아연, 산화마그네슘, 이산화규소, 비타민B6염산염</t>
+          <t>치자청색소, 오징어먹물색소, 락색소, 블루베리향, 라즈베리향, 복숭아향, 패션후르츠향, 딸기향, 이산화티타늄, 구연산, 프락토올리고당, 백설탕, 식품첨가물혼합제제</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>202608180976</t>
+          <t>202604216594</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -36896,22 +36896,22 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>20260818097</t>
+          <t>20260421659</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>자연담은 강진 단호박 쌀죽 만들기</t>
+          <t>캔디유 합격캔디 수제사탕</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>호렙농원</t>
+          <t>캔디유</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -36921,7 +36921,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>쌀가루, 서양호박분말, 설탕, 정제소금</t>
+          <t>백설탕, 프락토올리고당, 구연산, 이산화티타늄, 레몬향, 오징어먹물색소, 딸기향, 패션후르츠향, 복숭아향, 라임향, 치자황색소, 혼합제제, 치자청색소, 락색소</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -36933,7 +36933,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2026042183710</t>
+          <t>202604216593</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -36943,22 +36943,22 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>20260421837</t>
+          <t>20260421659</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>프리믹스O</t>
+          <t>캔디유 플라워믹스 수제사탕</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>(주)바인푸드</t>
+          <t>캔디유</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -36968,7 +36968,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>곡류가공품, 밀가루, 옥수수전분, 올레오레진캡시컴, 치자분말, L-글루탐산나트륨, 후추가루, 베이킹파우더, 폴리인산염, 정제소금</t>
+          <t>요거트향, 치자황색소, 치자황색소, 포도향, 요구르트향, 블루베리향, 이산화티타늄, 구연산, 프락토올리고당, 백설탕, 라임향, 딸기향, 레몬향, 혼합제제, 락색소</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -36980,7 +36980,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>202604218379</t>
+          <t>202604216595</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -36990,32 +36990,32 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>20260421837</t>
+          <t>20260421659</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>배터믹스</t>
+          <t>캔디유 후르츠믹스 수제사탕</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>(주)바인푸드</t>
+          <t>캔디유</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>터메릭올레오레진, 메틸셀룰로스, 정제소금, 밀가루</t>
+          <t>백설탕, 프락토올리고당, 구연산, 이산화티타늄, 치자황색소, 딸기향, 감귤향, 레몬향, 라임향, 복숭아향, 락색소, 치자청색소, 혼합제제</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -37027,7 +37027,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>202604218378</t>
+          <t>202604216592</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -37037,22 +37037,22 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>20260421837</t>
+          <t>20260421659</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>치킨파우더M</t>
+          <t>캔디유 사우어믹스 수제사탕</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>(주)바인푸드</t>
+          <t>캔디유</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -37062,7 +37062,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>터메릭올레오레진, L-글루탐산나트륨, 정제소금, 감자전분, 밀가루, 밀가루</t>
+          <t>락색소, 치자청색소, 감귤향, 라임향, 레몬향, 치자황색소, 이산화티타늄, 비타민C, 구연산, 프락토올리고당, 백설탕</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -37074,32 +37074,32 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>198604350131752</t>
+          <t>20260559122192</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>19860435013</t>
+          <t>20260559122</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>EVERYDAZE 그린 샐러드 크런치</t>
+          <t>수용성 커큐민 바이오페린</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>코스맥스바이오(주)</t>
+          <t>(주)코스모바이오</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -37109,54 +37109,54 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>채소혼합분말, 이산화규소, 스테아린산마그네슘, 구연산, DL-사과산, 비타민C, 효소처리스테비아, 토마토농축분말, 히드록시프로필메틸셀룰로스, 글리세린지방산에스테르, 이소말트, 치커리추출분말, D-소비톨, 덱스트린, 레몬향, 과일채소혼합분말</t>
+          <t>기타 농산가공품, 결정셀룰로스, 옥수수전분, 기타가공품, 고형차, 기타가공품, 과.채가공품, 비타민C, 이산화규소, 스테아린산마그네슘, 기타 농산가공품</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>199403722011688</t>
+          <t>20260559122194</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>19940372201</t>
+          <t>20260559122</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>살균당근분태</t>
+          <t>서리올맥스</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>인그린(주)</t>
+          <t>(주)코스모바이오</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>당근</t>
+          <t>기타가공품, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -37168,69 +37168,69 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>19950129282742</t>
+          <t>20260559122191</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>19950129282</t>
+          <t>20260559122</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>감자분말믹스A</t>
+          <t>리체르카 식물성 멜라토닌 함유 2mg</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>사조동아원(주) 부산공장</t>
+          <t>(주)코스모바이오</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>L-글루탐산나트륨, 감자분말, 메틸셀룰로스, 정제소금, 곡류가공품, 변성전분, 변성전분, 감자분말</t>
+          <t>기타 농산가공품, 과.채가공품, 기타가공품, 기타가공품, 고형차, 기타가공품, L-트립토판, 테아닌, 기타가공품, 가바, 혼합제제, 스테아린산마그네슘, 산화아연, 산화마그네슘, 이산화규소, 비타민B6염산염</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>19990623061328</t>
+          <t>202608180976</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>19990623061</t>
+          <t>20260818097</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>지리산 강황-하스카프베리시너지 환</t>
+          <t>자연담은 강진 단호박 쌀죽 만들기</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -37240,7 +37240,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>지리산홍화인</t>
+          <t>호렙농원</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -37250,54 +37250,54 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>댕댕이나무열매분말, 강황가루, 블루베리분말, 현미가루, 올리고당, 생강가루, 다시마분말, 천연후추(흑후추)향</t>
+          <t>쌀가루, 서양호박분말, 설탕, 정제소금</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>20030467230383</t>
+          <t>2026042183710</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>20030467230</t>
+          <t>20260421837</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>김오곤의황제침녹고프리미엄</t>
+          <t>프리믹스O</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>(주)대한홍삼진흥원</t>
+          <t>(주)바인푸드</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>식물혼합농축액, 홍삼향, 쌍화향, 불로초자실체농축액, 엿류</t>
+          <t>곡류가공품, 밀가루, 옥수수전분, 올레오레진캡시컴, 치자분말, L-글루탐산나트륨, 후추가루, 베이킹파우더, 폴리인산염, 정제소금</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -37309,22 +37309,22 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>20090458111424</t>
+          <t>202604218379</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>20090458111</t>
+          <t>20260421837</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>몰로키아추출분말</t>
+          <t>배터믹스</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -37334,17 +37334,17 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>(주)화인에프티</t>
+          <t>(주)바인푸드</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>몰로키아, 덱스트린, 아라비아검</t>
+          <t>터메릭올레오레진, 메틸셀룰로스, 정제소금, 밀가루</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -37356,42 +37356,42 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>20090458111423</t>
+          <t>202604218378</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>20090458111</t>
+          <t>20260421837</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>포멜로착즙분말</t>
+          <t>치킨파우더M</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>(주)화인에프티</t>
+          <t>(주)바인푸드</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>포멜로주스, 덱스트린, 아라비아검</t>
+          <t>터메릭올레오레진, L-글루탐산나트륨, 정제소금, 감자전분, 밀가루, 밀가루</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -37403,7 +37403,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2010014156681</t>
+          <t>198604350131752</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -37413,22 +37413,22 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>20100141566</t>
+          <t>19860435013</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>토큐환</t>
+          <t>EVERYDAZE 그린 샐러드 크런치</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>선용 바이오푸드</t>
+          <t>코스맥스바이오(주)</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -37438,7 +37438,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>토마토분말, 강황가루, 검정콩, 현미, L-아르지닌</t>
+          <t>채소혼합분말, 이산화규소, 스테아린산마그네슘, 구연산, DL-사과산, 비타민C, 효소처리스테비아, 토마토농축분말, 히드록시프로필메틸셀룰로스, 글리세린지방산에스테르, 이소말트, 치커리추출분말, D-소비톨, 덱스트린, 레몬향, 과일채소혼합분말</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -37450,7 +37450,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>20100365182198</t>
+          <t>199403722011688</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -37460,22 +37460,22 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>20100365182</t>
+          <t>19940372201</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>퓨어리서치 퓨어콜라겐</t>
+          <t>살균당근분태</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>(주)알피바이오</t>
+          <t>인그린(주)</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -37485,19 +37485,19 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>생선콜라겐펩타이드, 비타민C, 히알루론산, 향료, 대나무수액, 효소처리스테비아, 엘라스틴가수분해물, 비오틴</t>
+          <t>당근</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>20100515088804</t>
+          <t>19950129282742</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -37507,12 +37507,12 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>20100515088</t>
+          <t>19950129282</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>콤부차 식이섬유 핑크레몬</t>
+          <t>감자분말믹스A</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -37522,29 +37522,29 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>엔피케이(주)</t>
+          <t>사조동아원(주) 부산공장</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>자몽식이섬유, 유산균혼합분말, 수크랄로스, 기타가공품, 난소화성말토덱스트린(고시형), 구연산(무수), 에리스리톨, 생선콜라겐, 레몬엑기스분말, 레몬추출분말, 탄산수소나트륨, 기타가공품, 효소식품, 레몬향분말, 아스파탐, 비타민C, 파파야추출분말, 프락토올리고당, 대나무잎추출물, 치자적색소, 결정과당, 효소처리스테비아, 산화아연, 히알루론산혼합제제, 레몬식이섬유, 사과식이섬유</t>
+          <t>L-글루탐산나트륨, 감자분말, 메틸셀룰로스, 정제소금, 곡류가공품, 변성전분, 변성전분, 감자분말</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>20110444018198</t>
+          <t>19990623061328</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -37554,12 +37554,12 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>20110444018</t>
+          <t>19990623061</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>메타바이오 K</t>
+          <t>지리산 강황-하스카프베리시너지 환</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>바이셀</t>
+          <t>지리산홍화인</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -37579,19 +37579,19 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>에리스리톨, 난소화성말토덱스트린(고시형), 갈락토올리고당, 프락토올리고당, 프로바이오틱스(고시형), Lactiplantibacillus plantarum, 초유분말, 대나무수액, 유자향분말, 구연산(무수), Saccharomyces cerevisiae, 산화아연(고시형)</t>
+          <t>댕댕이나무열매분말, 강황가루, 블루베리분말, 현미가루, 올리고당, 생강가루, 다시마분말, 천연후추(흑후추)향</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>20110380845280</t>
+          <t>20030467230383</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -37601,44 +37601,44 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>20110380845</t>
+          <t>20030467230</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>프리미엄 미녀의 석류콜라겐 시즌3</t>
+          <t>김오곤의황제침녹고프리미엄</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>(주)메디언스 공장</t>
+          <t>(주)대한홍삼진흥원</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>엘라스틴, 히알루론산, 효모추출물, 혼합제제, 생선콜라겐, 석류농축액</t>
+          <t>식물혼합농축액, 홍삼향, 쌍화향, 불로초자실체농축액, 엿류</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>201104452921466</t>
+          <t>20090458111424</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -37648,22 +37648,22 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>20110445292</t>
+          <t>20090458111</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>바리스타시럽 블루큐라소</t>
+          <t>몰로키아추출분말</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>(주)흥국에프엔비</t>
+          <t>(주)화인에프티</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
@@ -37673,7 +37673,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>설탕, 천연향료, 소브산칼륨, 식용색소청색제1호, 정제수</t>
+          <t>몰로키아, 덱스트린, 아라비아검</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -37685,7 +37685,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>20120368372228</t>
+          <t>20090458111423</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -37695,12 +37695,12 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>20120368372</t>
+          <t>20090458111</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>딸기 스프레드</t>
+          <t>포멜로착즙분말</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>(주)유원</t>
+          <t>(주)화인에프티</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
@@ -37720,7 +37720,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>레시틴, 유청분말, 탈지분유, 설탕, 채종유(유채유 또는 카놀라유), 과.채가공품</t>
+          <t>포멜로주스, 덱스트린, 아라비아검</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -37732,7 +37732,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>201504612251578</t>
+          <t>2010014156681</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -37742,22 +37742,22 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>20150461225</t>
+          <t>20100141566</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>머위추출분말</t>
+          <t>토큐환</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>해찬솔푸드</t>
+          <t>선용 바이오푸드</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
@@ -37767,7 +37767,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>머위잎추출액, 덱스트린</t>
+          <t>토마토분말, 강황가루, 검정콩, 현미, L-아르지닌</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -37779,7 +37779,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>20170614111862</t>
+          <t>20100365182198</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -37789,22 +37789,22 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>20170614111</t>
+          <t>20100365182</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>홍도라지맥문동진액</t>
+          <t>퓨어리서치 퓨어콜라겐</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>(주)엔트리</t>
+          <t>(주)알피바이오</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -37814,19 +37814,19 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>액상차, 사철쑥, 대추, 작약뿌리, 복분자, 헛개나무열매, 지황, 계피, 감초, 불로초자실체, 익모초지상부, 생강, 황기, 참당귀, 천궁뿌리줄기, 올리고당, 기타과당, 카라멜색소 Ⅳ, 향료, 구연산</t>
+          <t>생선콜라겐펩타이드, 비타민C, 히알루론산, 향료, 대나무수액, 효소처리스테비아, 엘라스틴가수분해물, 비오틴</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>20170275127615</t>
+          <t>20100515088804</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -37836,22 +37836,22 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>20170275127</t>
+          <t>20100515088</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>엔칸토 카라멜시럽</t>
+          <t>콤부차 식이섬유 핑크레몬</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>주식회사 엔아이에프</t>
+          <t>엔피케이(주)</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -37861,19 +37861,19 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>향료, 소브산칼륨, 구연산, 설탕, 카라멜색소 Ⅲ, 정제수</t>
+          <t>자몽식이섬유, 유산균혼합분말, 수크랄로스, 기타가공품, 난소화성말토덱스트린(고시형), 구연산(무수), 에리스리톨, 생선콜라겐, 레몬엑기스분말, 레몬추출분말, 탄산수소나트륨, 기타가공품, 효소식품, 레몬향분말, 아스파탐, 비타민C, 파파야추출분말, 프락토올리고당, 대나무잎추출물, 치자적색소, 결정과당, 효소처리스테비아, 산화아연, 히알루론산혼합제제, 레몬식이섬유, 사과식이섬유</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>20180456001965</t>
+          <t>20110444018198</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -37883,22 +37883,22 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>20180456001</t>
+          <t>20110444018</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>레드비트착즙액</t>
+          <t>메타바이오 K</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>(주)가온에프앤비</t>
+          <t>바이셀</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -37908,7 +37908,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>레드비트뿌리</t>
+          <t>에리스리톨, 난소화성말토덱스트린(고시형), 갈락토올리고당, 프락토올리고당, 프로바이오틱스(고시형), Lactiplantibacillus plantarum, 초유분말, 대나무수액, 유자향분말, 구연산(무수), Saccharomyces cerevisiae, 산화아연(고시형)</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -37920,7 +37920,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2018049414328</t>
+          <t>20110380845280</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -37930,44 +37930,44 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>20180494143</t>
+          <t>20110380845</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>웨이크X100 큐민</t>
+          <t>프리미엄 미녀의 석류콜라겐 시즌3</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>바이오텐(주) 제2공장</t>
+          <t>(주)메디언스 공장</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>정제수, 스테비올배당체, 심황색소, 구연산(무수), 기타가공품, 난소화성말토덱스트린(고시형)</t>
+          <t>엘라스틴, 히알루론산, 효모추출물, 혼합제제, 생선콜라겐, 석류농축액</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2018036028143</t>
+          <t>201104452921466</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -37977,32 +37977,32 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>20180360281</t>
+          <t>20110445292</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>골든찹쌀치즈볼</t>
+          <t>바리스타시럽 블루큐라소</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>(주)골든팜</t>
+          <t>(주)흥국에프엔비</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>기타가공품, 치즈, 정제수, 설탕, 콩기름(대두유), 혼합제제</t>
+          <t>설탕, 천연향료, 소브산칼륨, 식용색소청색제1호, 정제수</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -38014,7 +38014,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>20180379618802</t>
+          <t>20120368372228</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -38024,22 +38024,22 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>20180379618</t>
+          <t>20120368372</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>삼사향액</t>
+          <t>딸기 스프레드</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>(주)세종바이오팜</t>
+          <t>(주)유원</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -38049,7 +38049,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>정제수, 삼씨앗추출액, 알리움후커리추출액, 기타가공품, 구연산</t>
+          <t>레시틴, 유청분말, 탈지분유, 설탕, 채종유(유채유 또는 카놀라유), 과.채가공품</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -38061,7 +38061,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2019032334466</t>
+          <t>201504612251578</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -38071,32 +38071,32 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>20190323344</t>
+          <t>20150461225</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>START 4 BLEND DAILY STICK</t>
+          <t>머위추출분말</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>팜앤브로 주식회사</t>
+          <t>해찬솔푸드</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>화분분말, 벌꿀, 로열젤리, 프로폴리스</t>
+          <t>머위잎추출액, 덱스트린</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -38108,7 +38108,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>20190189844126</t>
+          <t>20170614111862</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -38118,44 +38118,44 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>20190189844</t>
+          <t>20170614111</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>게라게이너</t>
+          <t>홍도라지맥문동진액</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>프로틴컴퍼니</t>
+          <t>(주)엔트리</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>곡류가공품, 기타가공품, 올리고당, 아미노산혼합분말, 비타민미네랄혼합분말, 비씨에이에이, L-아르지닌, 코코아분말, 수크랄로스, 효소처리스테비아, 식물성크림</t>
+          <t>액상차, 사철쑥, 대추, 작약뿌리, 복분자, 헛개나무열매, 지황, 계피, 감초, 불로초자실체, 익모초지상부, 생강, 황기, 참당귀, 천궁뿌리줄기, 올리고당, 기타과당, 카라멜색소 Ⅳ, 향료, 구연산</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>20200475051146</t>
+          <t>20170275127615</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -38165,32 +38165,32 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>20200475051</t>
+          <t>20170275127</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>크런치파우더</t>
+          <t>엔칸토 카라멜시럽</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>주식회사 SL푸드원</t>
+          <t>주식회사 엔아이에프</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>천연향신료, 천연향신료, 향료, 복합조미식품, 천연향신료, 기타 수산물가공품, 천연향신료, 향료제제, 기타가공품, 땅콩 또는 견과류가공품, 복합조미식품, 복합조미식품, 기타가공품, 중력분, 곡류가공품</t>
+          <t>향료, 소브산칼륨, 구연산, 설탕, 카라멜색소 Ⅲ, 정제수</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -38202,7 +38202,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>20200391559485</t>
+          <t>20180456001965</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -38212,32 +38212,32 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>20200391559</t>
+          <t>20180456001</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>강황분말</t>
+          <t>레드비트착즙액</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>(주)성진바이오 제1공장</t>
+          <t>(주)가온에프앤비</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>강황뿌리줄기</t>
+          <t>레드비트뿌리</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -38249,7 +38249,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2021048258136</t>
+          <t>2018049414328</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -38259,44 +38259,44 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>20210482581</t>
+          <t>20180494143</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>자연발효여주식초</t>
+          <t>웨이크X100 큐민</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>농업회사법인(유)꽃담길</t>
+          <t>바이오텐(주) 제2공장</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>여주, 설탕시럽</t>
+          <t>정제수, 스테비올배당체, 심황색소, 구연산(무수), 기타가공품, 난소화성말토덱스트린(고시형)</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>202102030783679</t>
+          <t>2018036028143</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -38306,32 +38306,32 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>20210203078</t>
+          <t>20180360281</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>젖산 마그네슘 99</t>
+          <t>골든찹쌀치즈볼</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>채움바이오 주식회사</t>
+          <t>(주)골든팜</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>기타가공품, 스테아린산마그네슘</t>
+          <t>기타가공품, 치즈, 정제수, 설탕, 콩기름(대두유), 혼합제제</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -38343,7 +38343,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>202102030783674</t>
+          <t>20180379618802</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -38353,44 +38353,44 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>20210203078</t>
+          <t>20180379618</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>무쿠픽 MGH 모노 글루코실 헤스페리딘</t>
+          <t>삼사향액</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>채움바이오 주식회사</t>
+          <t>(주)세종바이오팜</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>기타가공품, 스테아린산마그네슘</t>
+          <t>정제수, 삼씨앗추출액, 알리움후커리추출액, 기타가공품, 구연산</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>202102030783678</t>
+          <t>2019032334466</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -38400,44 +38400,44 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>20210203078</t>
+          <t>20190323344</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>마그네슘추출물</t>
+          <t>START 4 BLEND DAILY STICK</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>채움바이오 주식회사</t>
+          <t>팜앤브로 주식회사</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>기타가공품, 포도당, 덱스트린, 기타가공품, 기타가공품, 기타가공품, 프락토올리고당(고시형), 산화아연, 비타민C, 타우린, 테아닌, 비타민B6염산염, 혼합제제, 혼합제제, 이산화규소</t>
+          <t>화분분말, 벌꿀, 로열젤리, 프로폴리스</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>202102030783677</t>
+          <t>20190189844126</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -38447,12 +38447,12 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>20210203078</t>
+          <t>20190189844</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>마그네슘혼합분말</t>
+          <t>게라게이너</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -38462,17 +38462,17 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>채움바이오 주식회사</t>
+          <t>프로틴컴퍼니</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>산화마그네슘, 글루콘산마그네슘, 식품첨가물</t>
+          <t>곡류가공품, 기타가공품, 올리고당, 아미노산혼합분말, 비타민미네랄혼합분말, 비씨에이에이, L-아르지닌, 코코아분말, 수크랄로스, 효소처리스테비아, 식물성크림</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -38484,7 +38484,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>202102030783680</t>
+          <t>20200475051146</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -38494,12 +38494,12 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>20210203078</t>
+          <t>20200475051</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>(에스알)SR-07</t>
+          <t>크런치파우더</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -38509,17 +38509,17 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>채움바이오 주식회사</t>
+          <t>주식회사 SL푸드원</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>기타가공품, 덱스트린, 과.채가공품, 기타가공품, 프로바이오틱스분말(고시형)</t>
+          <t>천연향신료, 천연향신료, 향료, 복합조미식품, 천연향신료, 기타 수산물가공품, 천연향신료, 향료제제, 기타가공품, 땅콩 또는 견과류가공품, 복합조미식품, 복합조미식품, 기타가공품, 중력분, 곡류가공품</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -38531,7 +38531,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>202102030783681</t>
+          <t>20200391559485</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -38541,12 +38541,12 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>20210203078</t>
+          <t>20200391559</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>시크라온</t>
+          <t>강황분말</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -38556,17 +38556,17 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>채움바이오 주식회사</t>
+          <t>(주)성진바이오 제1공장</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>기타가공품, 과.채가공품, 결정셀룰로스, 기타가공품, 프락토올리고당(고시형), 이노시톨, 이산화규소, 스테아린산마그네슘, 식품첨가물혼합제제, 엽산</t>
+          <t>강황뿌리줄기</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -38578,7 +38578,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>202102030783676</t>
+          <t>2021048258136</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -38588,44 +38588,44 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>20210203078</t>
+          <t>20210482581</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>버닝 블랙커민 플러스 1200</t>
+          <t>자연발효여주식초</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>채움바이오 주식회사</t>
+          <t>농업회사법인(유)꽃담길</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>스테아린산마그네슘, 기타가공품</t>
+          <t>여주, 설탕시럽</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>202102030783675</t>
+          <t>202102030783679</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -38640,12 +38640,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>블랙커민추출물</t>
+          <t>젖산 마그네슘 99</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
@@ -38655,12 +38655,12 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>기타가공품, 난소화성말토덱스트린(고시형), 결정셀룰로스, 과.채가공품, 기타 농산가공품, 기타 농산가공품, 이산화규소, 과.채가공품, 식품첨가물혼합제제, 기타 농산가공품, 기타가공품, 비타민B6염산염</t>
+          <t>기타가공품, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -38672,7 +38672,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>202102030783672</t>
+          <t>202102030783674</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -38687,7 +38687,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>삼백초 아세로라정</t>
+          <t>무쿠픽 MGH 모노 글루코실 헤스페리딘</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -38702,12 +38702,12 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>기타가공품, 과.채가공품, 기타가공품, 과.채가공품, 비타민C, 이산화규소, 스테아린산마그네슘</t>
+          <t>기타가공품, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -38719,7 +38719,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>202102030783673</t>
+          <t>202102030783677</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -38734,7 +38734,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>모노글루코실헤스페리딘MGH</t>
+          <t>마그네슘혼합분말</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -38754,19 +38754,19 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>기타가공품, 난소화성말토덱스트린(고시형), 결정셀룰로스, 과.채가공품, 효소식품, 식품첨가물, 과.채가공품, 비타민C, 기타 농산가공품, 과.채가공품, 이산화규소, 케르세틴</t>
+          <t>산화마그네슘, 글루콘산마그네슘, 식품첨가물</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2021047919778</t>
+          <t>202102030783680</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -38776,12 +38776,12 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>20210479197</t>
+          <t>20210203078</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>리젠-씨 Regen-C</t>
+          <t>(에스알)SR-07</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -38791,7 +38791,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>(주)피비에이치바이오</t>
+          <t>채움바이오 주식회사</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -38801,7 +38801,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>에리스리톨, 자일리톨, 난소화성말토덱스트린(고시형), 효모식품, 비타민C, 과.채가공품, 기타가공품, 기타가공품, 혼합제제, 효소처리스테비아, 당류가공품, DL-사과산, 구연산(무수), 이산화규소, 니코틴산아미드, 혼합제제, 기타가공품, 고형차, 기타 수산물가공품, 기타가공품, 과.채가공품, 과.채가공품, 기타가공품, 과.채가공품, 기타 농산가공품, 기타 농산가공품, 베타인</t>
+          <t>기타가공품, 덱스트린, 과.채가공품, 기타가공품, 프로바이오틱스분말(고시형)</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -38813,7 +38813,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2022042325128</t>
+          <t>202102030783681</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -38823,44 +38823,44 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>20220423251</t>
+          <t>20210203078</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>비타온 글루타치온</t>
+          <t>시크라온</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>(주)한성헬시온</t>
+          <t>채움바이오 주식회사</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>기타가공품, 구연산(무수), 향료, 비타민C, 혼합제제, 과.채가공품, 기타 농산가공품, 당류가공품, 에리스리톨, 포도당, 이산화규소, 효소처리스테비아, 레드비트주스분말, 향료, DL-사과산, 향료, 기타 농산가공품, 히알루론산혼합제제, 기타가공품</t>
+          <t>기타가공품, 과.채가공품, 결정셀룰로스, 기타가공품, 프락토올리고당(고시형), 이노시톨, 이산화규소, 스테아린산마그네슘, 식품첨가물혼합제제, 엽산</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2022069602627</t>
+          <t>202102030783676</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -38870,22 +38870,22 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>20220696026</t>
+          <t>20210203078</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>파이토비탈릭스 지-파우 I</t>
+          <t>버닝 블랙커민 플러스 1200</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>(주)뉴트롬</t>
+          <t>채움바이오 주식회사</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
@@ -38895,7 +38895,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>기타가공품, 글리신</t>
+          <t>스테아린산마그네슘, 기타가공품</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -38907,7 +38907,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>20220520255201</t>
+          <t>202102030783675</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -38917,12 +38917,12 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>20220520255</t>
+          <t>20210203078</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>초유산양유단백질</t>
+          <t>블랙커민추출물</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -38932,7 +38932,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>아인팜</t>
+          <t>채움바이오 주식회사</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
@@ -38942,19 +38942,19 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>프락토올리고당, 유청칼슘, 유함유가공품, 혼합분유, 식물성크림, 생선콜라겐분말, 포도당, 유함유가공품, 유함유가공품, 분리대두단백, 덱스트린, 곡류가공품, 유청분말, 비타민미네랄혼합분말, 식품첨가물혼합제제, 효소처리스테비아</t>
+          <t>기타가공품, 난소화성말토덱스트린(고시형), 결정셀룰로스, 과.채가공품, 기타 농산가공품, 기타 농산가공품, 이산화규소, 과.채가공품, 식품첨가물혼합제제, 기타 농산가공품, 기타가공품, 비타민B6염산염</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>20220514509656</t>
+          <t>202102030783678</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -38964,44 +38964,44 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>20220514509</t>
+          <t>20210203078</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>바나린 포뮬러</t>
+          <t>마그네슘추출물</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>주식회사 예본바이오</t>
+          <t>채움바이오 주식회사</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>기타가공품, 과.채가공품, 건조효모(크롬함유), 기타가공품, 치커리뿌리추출물, 과.채가공품, 음료베이스, 기타가공품, 기타가공품, 구아검가수분해물(고시형), 기타가공품, 과.채가공품, 과.채가공품, 과.채가공품, 기타가공품, 유함유가공품, 건조효모(셀렌함유)</t>
+          <t>기타가공품, 포도당, 덱스트린, 기타가공품, 기타가공품, 기타가공품, 프락토올리고당(고시형), 산화아연, 비타민C, 타우린, 테아닌, 비타민B6염산염, 혼합제제, 혼합제제, 이산화규소</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>20220495001372</t>
+          <t>202102030783672</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -39011,22 +39011,22 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>20220495001</t>
+          <t>20210203078</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>어린이 초유 산양유 프리미엄 단백질</t>
+          <t>삼백초 아세로라정</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>(주)한미양행 선유공장</t>
+          <t>채움바이오 주식회사</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -39036,19 +39036,19 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>효소처리스테비아, 향료제제, 유청단백분말, 덱스트린, 코코아분말, 기타가공품, 결정과당, 두류가공품, 곡류가공품, 두류가공품, 유함유가공품, 초유단백분말, 기타가공품, 이산화규소, 혼합제제, 기타가공품, 기타가공품</t>
+          <t>기타가공품, 과.채가공품, 기타가공품, 과.채가공품, 비타민C, 이산화규소, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>20220495001371</t>
+          <t>202102030783673</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -39058,12 +39058,12 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>20220495001</t>
+          <t>20210203078</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>한미양행 더 뷰티 글루타치온</t>
+          <t>모노글루코실헤스페리딘MGH</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -39073,7 +39073,7 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>(주)한미양행 선유공장</t>
+          <t>채움바이오 주식회사</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -39083,19 +39083,19 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>향료, 혼합제제, 효모식품, 유함유가공품, 비타민C, 덱스트린, 포도당, 당류가공품, 기타가공품, L-시스틴, 기타가공품, 기타가공품, 판토텐산칼슘, 효소처리스테비아, 기타가공품, 이산화규소, 과.채가공품</t>
+          <t>기타가공품, 난소화성말토덱스트린(고시형), 결정셀룰로스, 과.채가공품, 효소식품, 식품첨가물, 과.채가공품, 비타민C, 기타 농산가공품, 과.채가공품, 이산화규소, 케르세틴</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2023052803288</t>
+          <t>2021047919778</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -39105,44 +39105,44 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>20230528032</t>
+          <t>20210479197</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>블랙웰곡물효소</t>
+          <t>리젠-씨 Regen-C</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>효소식품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>숭인내추럴팜(주) 제1공장</t>
+          <t>(주)피비에이치바이오</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>블루베리농축분말, 대두단백, 프락토올리고당, 식물성크림, 효소식품, 효소식품, 효소식품, 아로니아농축분말, 전분가공품, 유산균, 비타민C, 복분자엑기스분말, 라즈베리농축분말, 체리농축분말</t>
+          <t>에리스리톨, 자일리톨, 난소화성말토덱스트린(고시형), 효모식품, 비타민C, 과.채가공품, 기타가공품, 기타가공품, 혼합제제, 효소처리스테비아, 당류가공품, DL-사과산, 구연산(무수), 이산화규소, 니코틴산아미드, 혼합제제, 기타가공품, 고형차, 기타 수산물가공품, 기타가공품, 과.채가공품, 과.채가공품, 기타가공품, 과.채가공품, 기타 농산가공품, 기타 농산가공품, 베타인</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>효소</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2023024166127</t>
+          <t>2022042325128</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -39152,22 +39152,22 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>20230241661</t>
+          <t>20220423251</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>흑설탕양갱</t>
+          <t>비타온 글루타치온</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>꼬시식품</t>
+          <t>(주)한성헬시온</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -39177,19 +39177,19 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>한천, 물엿, 설탕, 조림류</t>
+          <t>기타가공품, 구연산(무수), 향료, 비타민C, 혼합제제, 과.채가공품, 기타 농산가공품, 당류가공품, 에리스리톨, 포도당, 이산화규소, 효소처리스테비아, 레드비트주스분말, 향료, DL-사과산, 향료, 기타 농산가공품, 히알루론산혼합제제, 기타가공품</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2023066113763</t>
+          <t>2022069602627</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -39199,44 +39199,44 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>20230661137</t>
+          <t>20220696026</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>도라지청 A</t>
+          <t>파이토비탈릭스 지-파우 I</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>세종에프앤비 주식회사</t>
+          <t>(주)뉴트롬</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>사양벌꿀, 물엿, 액상과당, 도라지뿌리추출액</t>
+          <t>기타가공품, 글리신</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2024067608840</t>
+          <t>20220520255201</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -39246,12 +39246,12 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>20240676088</t>
+          <t>20220520255</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>쫀득 감자볼</t>
+          <t>초유산양유단백질</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -39261,29 +39261,29 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>(주)맘모스식품</t>
+          <t>아인팜</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>감자, 전분가공품, 콩기름(대두유), 복합조미식품</t>
+          <t>프락토올리고당, 유청칼슘, 유함유가공품, 혼합분유, 식물성크림, 생선콜라겐분말, 포도당, 유함유가공품, 유함유가공품, 분리대두단백, 덱스트린, 곡류가공품, 유청분말, 비타민미네랄혼합분말, 식품첨가물혼합제제, 효소처리스테비아</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2025020310873</t>
+          <t>20220514509656</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -39293,22 +39293,22 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>20250203108</t>
+          <t>20220514509</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>디엑시 프로</t>
+          <t>바나린 포뮬러</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>주식회사 지니바이오</t>
+          <t>주식회사 예본바이오</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -39318,7 +39318,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>기타가공품, 덱스트린, 결정셀룰로스, 생선콜라겐펩타이드, 기타가공품, L-시스틴, 아미노산혼합제제, 비오틴, 이산화규소, 스테아린산마그네슘</t>
+          <t>기타가공품, 과.채가공품, 건조효모(크롬함유), 기타가공품, 치커리뿌리추출물, 과.채가공품, 음료베이스, 기타가공품, 기타가공품, 구아검가수분해물(고시형), 기타가공품, 과.채가공품, 과.채가공품, 과.채가공품, 기타가공품, 유함유가공품, 건조효모(셀렌함유)</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -39330,7 +39330,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2025078331912</t>
+          <t>202206834731795</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -39340,32 +39340,32 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>20250783319</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>수제 깻잎전</t>
+          <t>빌베리 복합 분말</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>농업회사법인 바잘농산물 주식회사</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>돼지고기, 두부, 양파, 계란, 들깻잎, 밀가루, 당근, 대파, 콩기름(대두유), 마늘, 정제소금, 후추가루</t>
+          <t>식품첨가물, 기타가공품, 기타가공품, 기타가공품, 식품첨가물, 포도당, 과.채가공품</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -39377,7 +39377,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>202507833199</t>
+          <t>202206834731792</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -39387,44 +39387,44 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>20250783319</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>수제 소고기육전</t>
+          <t>리베온 베르베린 복합물</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>농업회사법인 바잘농산물 주식회사</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>정제소금, 콩기름(대두유), 밀가루, 소고기, 계란, 마늘, 후추가루, 정제수</t>
+          <t>이눌린/치커리추출물(고시형), 효모식품, 식품첨가물, 바나바잎 추출물(고시형), 기타가공품, 식품첨가물, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품, 식품첨가물, 두류가공품, 올리고당, 난소화성말토덱스트린(고시형), 식품첨가물</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2025078331910</t>
+          <t>202206834731798</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -39434,32 +39434,32 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>20250783319</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>수제 꼬지전</t>
+          <t>니프로젠 알파 스파이크 플러스</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>농업회사법인 바잘농산물 주식회사</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>햄, M맛살, 절임무청, 계란, 파, 밀가루, 콩기름(대두유), 정제수, 정제소금, 설탕, 후추가루</t>
+          <t>식품첨가물, 올리고당, 구아검가수분해물(고시형), 기타가공품, 과.채가공품, 난소화성말토덱스트린(고시형), 식품첨가물, 기타가공품, 기타가공품, 기타가공품, 식품첨가물</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -39471,7 +39471,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>202505045518</t>
+          <t>202206834731794</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -39481,12 +39481,12 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>20250504551</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>말차양갱</t>
+          <t>하이제닉스 HIGHGENIX</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -39496,17 +39496,17 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>(주)대조에프앤비 제2공장</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>정제수, 백설탕, 당류가공품, 땅콩 또는 견과류가공품, 고형차, 한천, 정제소금, 합성향료, 조림류</t>
+          <t>식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 식품첨가물혼합제제, 유함유가공품, 식품첨가물, 기타가공품, 효소처리스테비아, 식품첨가물, 유함유가공품, 유함유가공품, 식품첨가물, 식품첨가물, 유함유가공품, 덱스트린, 기타가공품, 포도당, 식품첨가물혼합제제, 과.채가공품</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -39518,7 +39518,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>202505045519</t>
+          <t>202206834731796</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -39528,32 +39528,32 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>20250504551</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>한라봉양갱</t>
+          <t>비전복합물i</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>(주)대조에프앤비 제2공장</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>정제소금, 합성향료, 한천, 과.채가공품, 조림류, 정제수, 백설탕, 당류가공품, 과.채가공품</t>
+          <t>기타가공품, 효소식품, 기타가공품, 과.채가공품, 기타가공품, 과.채가공품, 덱스트린, 식품첨가물, 식품첨가물, 과.채가공품, 올리고당, 식품첨가물, 이눌린/치커리추출물(고시형), 과.채가공품</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -39565,7 +39565,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>202508141377</t>
+          <t>202206834731788</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -39575,44 +39575,44 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>20250814137</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>레몬착즙원액</t>
+          <t>알파CD 브로멜라인 복합물</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>장성레몬 우성영농조합법인</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>레몬과립</t>
+          <t>식품첨가물, 효소식품, 기타가공품, 기타가공품, 고형차, 기타가공품, 효소식품, 과.채가공품, 식품첨가물, 식품첨가물, 덱스트린, 난소화성말토덱스트린(고시형), 이눌린(고시형)</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>다이어트</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>202607280661</t>
+          <t>202206834731799</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -39622,32 +39622,32 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>20260728066</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>태을순맥 진</t>
+          <t>루버스코어복분자혼합분말</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>신성푸드텍</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>정제수, 비수리, 황기뿌리, 단삼뿌리, 참당귀</t>
+          <t>기타가공품, 식품첨가물, 고형차, 식품첨가물, 식품첨가물, 포도당, 기타가공품, 과.채가공품, 덱스트린, 식품첨가물, 이눌린/치커리추출물(고시형)</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -39659,7 +39659,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>20260559122197</t>
+          <t>202206834731790</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -39669,69 +39669,69 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>20260559122</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>비타허브 그린 아세로라 비타민C</t>
+          <t>젖산마그네슘 복합분말</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>(주)코스모바이오</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>스테아린산마그네슘, 이산화규소, 기타가공품</t>
+          <t>식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 당류가공품, 이눌린/치커리추출물(고시형), 식품첨가물, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>198604350131754</t>
+          <t>20220495001372</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>19860435013</t>
+          <t>20220495001</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>엔플 탭 클렌즈</t>
+          <t>어린이 초유 산양유 프리미엄 단백질</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>코스맥스바이오(주)</t>
+          <t>(주)한미양행 선유공장</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -39741,44 +39741,44 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>중쇄중성지방유, 치자청색소, 히드록시프로필메틸셀룰로스, 비트레드, 치자황색소, 트로피칼후르츠믹스향분말, 청사과향, 효소처리스테비아, DL-사과산, 파인애플향, 스테아린산마그네슘, 이산화규소, 목화씨기름, 결정셀룰로스, 식초분말, 토마토식초, D-소비톨, 이소말트, 식초분말</t>
+          <t>효소처리스테비아, 향료제제, 유청단백분말, 덱스트린, 코코아분말, 기타가공품, 결정과당, 두류가공품, 곡류가공품, 두류가공품, 유함유가공품, 초유단백분말, 기타가공품, 이산화규소, 혼합제제, 기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>19960372607575</t>
+          <t>20220495001371</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>19960372607</t>
+          <t>20220495001</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>에이지스클리어 포뮬러</t>
+          <t>한미양행 더 뷰티 글루타치온</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>(주)네추럴웨이</t>
+          <t>(주)한미양행 선유공장</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -39788,101 +39788,101 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>과.채가공품, 구기자추출물분말, 배초향추출분말, 포도당</t>
+          <t>향료, 혼합제제, 효모식품, 유함유가공품, 비타민C, 덱스트린, 포도당, 당류가공품, 기타가공품, L-시스틴, 기타가공품, 기타가공품, 판토텐산칼슘, 효소처리스테비아, 기타가공품, 이산화규소, 과.채가공품</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>20000467059369</t>
+          <t>2023052803288</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>20230528032</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>블랙웰곡물효소</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>효소식품</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>숭인내추럴팜(주) 제1공장</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>20000467059</t>
-        </is>
-      </c>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>모과엑기스분말</t>
-        </is>
-      </c>
-      <c r="E588" t="inlineStr">
-        <is>
-          <t>과.채가공품</t>
-        </is>
-      </c>
-      <c r="F588" t="inlineStr">
-        <is>
-          <t>(주)후드코리아</t>
-        </is>
-      </c>
-      <c r="G588" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>모과엑기스, 덱스트린</t>
+          <t>블루베리농축분말, 대두단백, 프락토올리고당, 식물성크림, 효소식품, 효소식품, 효소식품, 아로니아농축분말, 전분가공품, 유산균, 비타민C, 복분자엑기스분말, 라즈베리농축분말, 체리농축분말</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>20020461444714</t>
+          <t>2023024166127</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>20230241661</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>흑설탕양갱</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>꼬시식품</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>20020461444</t>
-        </is>
-      </c>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>젤리핑 깡총핑</t>
-        </is>
-      </c>
-      <c r="E589" t="inlineStr">
-        <is>
-          <t>캔디류</t>
-        </is>
-      </c>
-      <c r="F589" t="inlineStr">
-        <is>
-          <t>데코리아제과(주)</t>
-        </is>
-      </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>설탕, 물엿, 정제수, 펙틴, 구연산, 구연산삼나트륨, 향료, 혼합제제, 치자청색소, 홍화황색소, 젤라틴, 가공유지</t>
+          <t>한천, 물엿, 설탕, 조림류</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -39894,126 +39894,126 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>20020461444713</t>
+          <t>2023066113763</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>20230661137</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>도라지청 A</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>세종에프앤비 주식회사</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>20020461444</t>
-        </is>
-      </c>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>젤리핑 하츄핑</t>
-        </is>
-      </c>
-      <c r="E590" t="inlineStr">
-        <is>
-          <t>캔디류</t>
-        </is>
-      </c>
-      <c r="F590" t="inlineStr">
-        <is>
-          <t>데코리아제과(주)</t>
-        </is>
-      </c>
-      <c r="G590" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>혼합제제, 향료, 구연산삼나트륨, 구연산, 펙틴, 정제수, 물엿, 설탕, 가공유지, 젤라틴, 홍화황색소, 치자청색소</t>
+          <t>사양벌꿀, 물엿, 액상과당, 도라지뿌리추출액</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>201504420251381</t>
+          <t>2024067608840</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>20150442025</t>
+          <t>20240676088</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>오미자추출액HR-6175</t>
+          <t>쫀득 감자볼</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>주식회사 하람</t>
+          <t>(주)맘모스식품</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>오미자열매, 정제수</t>
+          <t>감자, 전분가공품, 콩기름(대두유), 복합조미식품</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>20160445053670</t>
+          <t>2025020310873</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>20160445053</t>
+          <t>20250203108</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>마늘부스터(어묵스프용)</t>
+          <t>디엑시 프로</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>(주)성보 대소공장</t>
+          <t>주식회사 지니바이오</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
@@ -40023,7 +40023,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>5-리보뉴클레오티드이나트륨, 천연향신료, 이산화규소, 과.채가공품</t>
+          <t>기타가공품, 덱스트린, 결정셀룰로스, 생선콜라겐펩타이드, 기타가공품, L-시스틴, 아미노산혼합제제, 비오틴, 이산화규소, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -40035,42 +40035,42 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2017044400819</t>
+          <t>2025078331912</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>20250783319</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>수제 깻잎전</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>농업회사법인 바잘농산물 주식회사</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>20170444008</t>
-        </is>
-      </c>
-      <c r="D593" t="inlineStr">
-        <is>
-          <t>애플사이다비니거 스틱</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr">
-        <is>
-          <t>발효식초</t>
-        </is>
-      </c>
-      <c r="F593" t="inlineStr">
-        <is>
-          <t>주식회사 케이바이오</t>
-        </is>
-      </c>
-      <c r="G593" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>돼지고기, 두부, 양파, 계란, 들깻잎, 밀가루, 당근, 대파, 콩기름(대두유), 마늘, 정제소금, 후추가루</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -40082,89 +40082,89 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2017020960325</t>
+          <t>202507833199</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>20250783319</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>수제 소고기육전</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>농업회사법인 바잘농산물 주식회사</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>20170209603</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>바이탈코리아G</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr">
-        <is>
-          <t>기타가공품</t>
-        </is>
-      </c>
-      <c r="F594" t="inlineStr">
-        <is>
-          <t>(주)바이탈코리아</t>
-        </is>
-      </c>
-      <c r="G594" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>효모식품, 타우린, 치커리뿌리추출물분말, 난소화성말토덱스트린(고시형)</t>
+          <t>정제소금, 콩기름(대두유), 밀가루, 소고기, 계란, 마늘, 후추가루, 정제수</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>피로개선</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>20180042191557</t>
+          <t>2025078331910</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>20250783319</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>수제 꼬지전</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>농업회사법인 바잘농산물 주식회사</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>20180042191</t>
-        </is>
-      </c>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>쇠비름(마치현)분말</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>고형차</t>
-        </is>
-      </c>
-      <c r="F595" t="inlineStr">
-        <is>
-          <t>주식회사 더좋은네이처</t>
-        </is>
-      </c>
-      <c r="G595" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>쇠비름</t>
+          <t>햄, M맛살, 절임무청, 계란, 파, 밀가루, 콩기름(대두유), 정제수, 정제소금, 설탕, 후추가루</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -40176,42 +40176,42 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>20180042191556</t>
+          <t>202505045518</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>20250504551</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>말차양갱</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>(주)대조에프앤비 제2공장</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>20180042191</t>
-        </is>
-      </c>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>쇠비름(마치현)환</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>기타가공품</t>
-        </is>
-      </c>
-      <c r="F596" t="inlineStr">
-        <is>
-          <t>주식회사 더좋은네이처</t>
-        </is>
-      </c>
-      <c r="G596" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>쇠비름, 밀</t>
+          <t>정제수, 백설탕, 당류가공품, 땅콩 또는 견과류가공품, 고형차, 한천, 정제소금, 합성향료, 조림류</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -40223,69 +40223,69 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>20180442157208</t>
+          <t>202505045519</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>20250504551</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>한라봉양갱</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>(주)대조에프앤비 제2공장</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
           <t>20260910</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>20180442157</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>프로폴리스 덴티프레시 구강유산균</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>캔디류</t>
-        </is>
-      </c>
-      <c r="F597" t="inlineStr">
-        <is>
-          <t>(주)메디오젠충주공장</t>
-        </is>
-      </c>
-      <c r="G597" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>혼합제제, Lacticaseibacillus rhamnosus(고시형), 혼합제제, D-소비톨, 이소말트, 구연산, 스테아린산마그네슘, 프락토올리고당(고시형), 혼합제제, 기타가공품, 기타 수산물가공품, 프로폴리스추출물(고시형), 락토페린농축물, 프로바이오틱스(고시형)</t>
+          <t>정제소금, 합성향료, 한천, 과.채가공품, 조림류, 정제수, 백설탕, 당류가공품, 과.채가공품</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>20180355577300</t>
+          <t>202508141377</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>20180355577</t>
+          <t>20250814137</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>고이밤</t>
+          <t>레몬착즙원액</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -40295,7 +40295,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>(주)정담푸드</t>
+          <t>장성레몬 우성영농조합법인</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
@@ -40305,44 +40305,44 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>식품첨가물, 프락토올리고당, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 액상차</t>
+          <t>레몬과립</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>20190326100512</t>
+          <t>202607280661</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>20190326100</t>
+          <t>20260728066</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>미라클 산호</t>
+          <t>태을순맥 진</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>우리바이오 주식회사</t>
+          <t>신성푸드텍</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
@@ -40352,7 +40352,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>이산화규소, 정제소금, 산호분말, 젖산칼슘, 글루콘산마그네슘, 분말결정포도당, 비타민D3혼합제제</t>
+          <t>정제수, 비수리, 황기뿌리, 단삼뿌리, 참당귀</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -40364,22 +40364,22 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>201904915485</t>
+          <t>20260559122197</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>20190491548</t>
+          <t>20260559122</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>아이스투미츄유자</t>
+          <t>비타허브 그린 아세로라 비타민C</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -40389,7 +40389,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>농업회사법인(주) 올과</t>
+          <t>(주)코스모바이오</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -40399,19 +40399,19 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>백설탕, 정제수, 오렌지주스, 유자청</t>
+          <t>스테아린산마그네슘, 이산화규소, 기타가공품</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>20190498210523</t>
+          <t>198604350131754</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -40421,32 +40421,32 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>20190498210</t>
+          <t>19860435013</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>포마더 파바톤 슬로우에이지 워터믹스 저당</t>
+          <t>엔플 탭 클렌즈</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>(주)한풍네이처팜</t>
+          <t>코스맥스바이오(주)</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>시클로덱스트린, 난소화성말토덱스트린분말(고시형), 기타가공품, 구연산(무수), 기타가공품, 자몽농축분말, 향료, 식품첨가물, 비타민C, 효소처리스테비아, 글루콘산아연, 건조효모(셀렌함유), 푸마르산제일철, 아스파탐, 스테비올배당체, 비타민B12, 혼합제제, 비타민B6염산염, 엽산</t>
+          <t>중쇄중성지방유, 치자청색소, 히드록시프로필메틸셀룰로스, 비트레드, 치자황색소, 트로피칼후르츠믹스향분말, 청사과향, 효소처리스테비아, DL-사과산, 파인애플향, 스테아린산마그네슘, 이산화규소, 목화씨기름, 결정셀룰로스, 식초분말, 토마토식초, D-소비톨, 이소말트, 식초분말</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -40458,7 +40458,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>20200467503794</t>
+          <t>19960372607575</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -40468,32 +40468,32 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>20200467503</t>
+          <t>19960372607</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>딸기과즙농축액S</t>
+          <t>에이지스클리어 포뮬러</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>올담식품</t>
+          <t>(주)네추럴웨이</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>딸기농축액, 물엿</t>
+          <t>과.채가공품, 구기자추출물분말, 배초향추출분말, 포도당</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -40505,7 +40505,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2020045111634</t>
+          <t>20000467059369</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -40515,22 +40515,22 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>20200451116</t>
+          <t>20000467059</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>소야</t>
+          <t>모과엑기스분말</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>(주)아비스모 생활건강</t>
+          <t>(주)후드코리아</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
@@ -40540,19 +40540,19 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>벌꿀, 올리고당, 발효대두, 볶은현미, 볶은우엉, 볶은둥굴레, 오미자열매, 모창출뿌리줄기, 복령균핵</t>
+          <t>모과엑기스, 덱스트린</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>20210519071220</t>
+          <t>20020461444713</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -40562,32 +40562,32 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>20210519071</t>
+          <t>20020461444</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>산수유큐민</t>
+          <t>젤리핑 하츄핑</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>엔피케이(주) 2공장</t>
+          <t>데코리아제과(주)</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>산수유추출액, 기타가공품</t>
+          <t>혼합제제, 향료, 구연산삼나트륨, 구연산, 펙틴, 정제수, 물엿, 설탕, 가공유지, 젤라틴, 홍화황색소, 치자청색소</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -40599,7 +40599,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>20220820077176</t>
+          <t>20020461444714</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -40609,44 +40609,44 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>20220820077</t>
+          <t>20020461444</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>평온한밤 식물성 멜라토닌</t>
+          <t>젤리핑 깡총핑</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>주식회사 에이원바이옴</t>
+          <t>데코리아제과(주)</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>난백분, 기타가공품, 이산화규소, 기타가공품, 땅콩 또는 견과류가공품, 이눌린/치커리추출물(고시형), 스테아린산마그네슘, 효모식품, 히드록시프로필메틸셀룰로스, 식품첨가물</t>
+          <t>설탕, 물엿, 정제수, 펙틴, 구연산, 구연산삼나트륨, 향료, 혼합제제, 치자청색소, 홍화황색소, 젤라틴, 가공유지</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>20220820077177</t>
+          <t>201504420251381</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -40656,22 +40656,22 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>20220820077</t>
+          <t>20150442025</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>타트체리복합분말</t>
+          <t>오미자추출액HR-6175</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>주식회사 에이원바이옴</t>
+          <t>주식회사 하람</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
@@ -40681,19 +40681,19 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>포도당, 과.채가공품</t>
+          <t>오미자열매, 정제수</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>20230268165163</t>
+          <t>20160445053670</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -40703,12 +40703,12 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>20230268165</t>
+          <t>20160445053</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>고단백 얌얌쉐이크 딥밀크맛</t>
+          <t>마늘부스터(어묵스프용)</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -40718,29 +40718,29 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>그린스퀘어(주)</t>
+          <t>(주)성보 대소공장</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>알룰로오스, 에리스리톨, 글리신, 효소처리스테비아, 혼합제제, 초콜릿가공품, 향료제제, 혼합제제, 가공유크림, 전지분유, 유청단백분말, 기타가공품, 두류가공품, 유함유가공품, 난소화성말토덱스트린(고시형), 정제소금</t>
+          <t>5-리보뉴클레오티드이나트륨, 천연향신료, 이산화규소, 과.채가공품</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>20230281157121</t>
+          <t>2017044400819</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -40750,22 +40750,22 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>20230281157</t>
+          <t>20170444008</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>자연명가 당류 0% 진짜 무당 생강청 국내산(100%) 생강</t>
+          <t>애플사이다비니거 스틱</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>티디바인</t>
+          <t>주식회사 케이바이오</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
@@ -40775,7 +40775,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>생강추출액, 알룰로오스, 생강농축액, 아라비아검, 효소처리스테비아, 폴리덱스트로스, 난소화성말토덱스트린(고시형)</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -40787,7 +40787,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>20230609874607</t>
+          <t>2017020960325</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -40797,44 +40797,44 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>20230609874</t>
+          <t>20170209603</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>프라임 폴리코사놀20</t>
+          <t>바이탈코리아G</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>(주)뉴트리션바이오</t>
+          <t>(주)바이탈코리아</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>프락토올리고당, 치커리추출분말, 결정셀룰로스, 기타가공품, 해조혼합분말, 이산화규소, 스테아린산마그네슘, 녹차추출물분말(고시형), 클로렐라분말, 스피루리나, 기타 농산가공품, 귀리식이섬유, 레몬밤분말, 효모식품</t>
+          <t>효모식품, 타우린, 치커리뿌리추출물분말, 난소화성말토덱스트린(고시형)</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>피로개선</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>20230609874608</t>
+          <t>20180042191556</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -40844,44 +40844,44 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>20230609874</t>
+          <t>20180042191</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>폴리코사놀 스타트</t>
+          <t>쇠비름(마치현)환</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>(주)뉴트리션바이오</t>
+          <t>주식회사 더좋은네이처</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>녹차추출물분말(고시형), 프락토올리고당, 치커리추출분말, 결정셀룰로스, 기타가공품, 해조혼합분말, 이산화규소, 스테아린산마그네슘, 기타 농산가공품, 스피루리나, 클로렐라분말, 귀리식이섬유, 레몬밤분말, 효모식품, 니코틴산아미드</t>
+          <t>쇠비름, 밀</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>20240658113240</t>
+          <t>20180042191557</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -40891,44 +40891,44 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>20240658113</t>
+          <t>20180042191</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>트리코바이옴MG901사균체</t>
+          <t>쇠비름(마치현)분말</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>(주)메디오젠</t>
+          <t>주식회사 더좋은네이처</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>덱스트린, Limosilactobacillus fermentum</t>
+          <t>쇠비름</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2024057720624</t>
+          <t>20180442157208</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -40938,44 +40938,44 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>20240577206</t>
+          <t>20180442157</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>보스웰리아한방복합물SA</t>
+          <t>프로폴리스 덴티프레시 구강유산균</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>상아생명과학주식회사 F1</t>
+          <t>(주)메디오젠충주공장</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>기타가공품, 기타가공품</t>
+          <t>혼합제제, Lacticaseibacillus rhamnosus(고시형), 혼합제제, D-소비톨, 이소말트, 구연산, 스테아린산마그네슘, 프락토올리고당(고시형), 혼합제제, 기타가공품, 기타 수산물가공품, 프로폴리스추출물(고시형), 락토페린농축물, 프로바이오틱스(고시형)</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>202605273108</t>
+          <t>20180355577300</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -40985,22 +40985,22 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>20260527310</t>
+          <t>20180355577</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>굴림곶감</t>
+          <t>고이밤</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>현대무브 주식회사</t>
+          <t>(주)정담푸드</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
@@ -41010,7 +41010,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>사양벌꿀, 천연향신료, 버터, 잣, 곶감, 정제소금</t>
+          <t>식품첨가물, 프락토올리고당, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 액상차</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -41022,89 +41022,89 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>20110568038376</t>
+          <t>20190326100512</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>20110568038</t>
+          <t>20190326100</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>단백질혼합분말F3</t>
+          <t>미라클 산호</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>주식회사 오그래 농업회사법인</t>
+          <t>우리바이오 주식회사</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>수크랄로스, 향료, 아몬드분말, 이집트콩분말, 난소화성말토덱스트린(고시형), 유청단백분말, 식물성크림</t>
+          <t>이산화규소, 정제소금, 산호분말, 젖산칼슘, 글루콘산마그네슘, 분말결정포도당, 비타민D3혼합제제</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>20110568038377</t>
+          <t>201904915485</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>20190491548</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>아이스투미츄유자</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>농업회사법인(주) 올과</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
           <t>20260911</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>20110568038</t>
-        </is>
-      </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>단백한끼 더블크런치 토피넛라떼</t>
-        </is>
-      </c>
-      <c r="E615" t="inlineStr">
-        <is>
-          <t>기타가공품</t>
-        </is>
-      </c>
-      <c r="F615" t="inlineStr">
-        <is>
-          <t>주식회사 오그래 농업회사법인</t>
-        </is>
-      </c>
-      <c r="G615" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>아몬드, 분리대두단백, 젤라틴, 기타가공품, 복합조미식품, 효소처리스테비아, 분말유크림, 기타소금, 커피, 탈지땅콩분말, 향료, 코코아분말, 탈지분유, 식물성크림, 혼합제제, 곡류가공품, 과자, 혼합제제, 비타민미네랄혼합제제, 과자, 곡류가공품, 곡류가공품</t>
+          <t>백설탕, 정제수, 오렌지주스, 유자청</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -41116,89 +41116,89 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2014015210850</t>
+          <t>20190498210523</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>20190498210</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>포마더 파바톤 슬로우에이지 워터믹스 저당</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>(주)한풍네이처팜</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
           <t>20260911</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>20140152108</t>
-        </is>
-      </c>
-      <c r="D616" t="inlineStr">
-        <is>
-          <t>후레쉬코</t>
-        </is>
-      </c>
-      <c r="E616" t="inlineStr">
-        <is>
-          <t>기타가공품</t>
-        </is>
-      </c>
-      <c r="F616" t="inlineStr">
-        <is>
-          <t>(주)지엠생명공학</t>
-        </is>
-      </c>
-      <c r="G616" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>정제수, 보스웰리아추출물, 은행잎추출물, 감초추출액, 지치뿌리추출물, 천궁추출액, 칡발효액, 박하추출물, 목련꽃잎, 퉁퉁마디추출액</t>
+          <t>시클로덱스트린, 난소화성말토덱스트린분말(고시형), 기타가공품, 구연산(무수), 기타가공품, 자몽농축분말, 향료, 식품첨가물, 비타민C, 효소처리스테비아, 글루콘산아연, 건조효모(셀렌함유), 푸마르산제일철, 아스파탐, 스테비올배당체, 비타민B12, 혼합제제, 비타민B6염산염, 엽산</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>20170474140102</t>
+          <t>20200467503794</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>20170474140</t>
+          <t>20200467503</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>고로케 속재료</t>
+          <t>딸기과즙농축액S</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>뜰방네</t>
+          <t>올담식품</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>양배추, 돼지고기, 감자, 양파, 당근, 파, 당면, 마가린, 카레, 간장, 소스, 가공소금, 후추가루</t>
+          <t>딸기농축액, 물엿</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -41210,92 +41210,797 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>20190478227182</t>
+          <t>2020045111634</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>20200451116</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>소야</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>(주)아비스모 생활건강</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
           <t>20260911</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>20190478227</t>
-        </is>
-      </c>
-      <c r="D618" t="inlineStr">
-        <is>
-          <t>천라수 효소액</t>
-        </is>
-      </c>
-      <c r="E618" t="inlineStr">
-        <is>
-          <t>액상차</t>
-        </is>
-      </c>
-      <c r="F618" t="inlineStr">
-        <is>
-          <t>농업회사법인내포주식회사</t>
-        </is>
-      </c>
-      <c r="G618" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>수세미오이어린열매발효농축액, 설탕</t>
+          <t>벌꿀, 올리고당, 발효대두, 볶은현미, 볶은우엉, 볶은둥굴레, 오미자열매, 모창출뿌리줄기, 복령균핵</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>효소</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
+          <t>20210519071220</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>20210519071</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>산수유큐민</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>엔피케이(주) 2공장</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>산수유추출액, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>20220820077177</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>20220820077</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>타트체리복합분말</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>주식회사 에이원바이옴</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>포도당, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>20220820077176</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>20220820077</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>평온한밤 식물성 멜라토닌</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>주식회사 에이원바이옴</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>난백분, 기타가공품, 이산화규소, 기타가공품, 땅콩 또는 견과류가공품, 이눌린/치커리추출물(고시형), 스테아린산마그네슘, 효모식품, 히드록시프로필메틸셀룰로스, 식품첨가물</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>수면</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>20230268165163</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>20230268165</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>고단백 얌얌쉐이크 딥밀크맛</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>그린스퀘어(주)</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>알룰로오스, 에리스리톨, 글리신, 효소처리스테비아, 혼합제제, 초콜릿가공품, 향료제제, 혼합제제, 가공유크림, 전지분유, 유청단백분말, 기타가공품, 두류가공품, 유함유가공품, 난소화성말토덱스트린(고시형), 정제소금</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>20230281157121</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>20230281157</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>자연명가 당류 0% 진짜 무당 생강청 국내산(100%) 생강</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>티디바인</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>생강추출액, 알룰로오스, 생강농축액, 아라비아검, 효소처리스테비아, 폴리덱스트로스, 난소화성말토덱스트린(고시형)</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>20230609874607</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>20230609874</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>프라임 폴리코사놀20</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>(주)뉴트리션바이오</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>프락토올리고당, 치커리추출분말, 결정셀룰로스, 기타가공품, 해조혼합분말, 이산화규소, 스테아린산마그네슘, 녹차추출물분말(고시형), 클로렐라분말, 스피루리나, 기타 농산가공품, 귀리식이섬유, 레몬밤분말, 효모식품</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>20230609874608</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>20230609874</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>폴리코사놀 스타트</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>(주)뉴트리션바이오</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>녹차추출물분말(고시형), 프락토올리고당, 치커리추출분말, 결정셀룰로스, 기타가공품, 해조혼합분말, 이산화규소, 스테아린산마그네슘, 기타 농산가공품, 스피루리나, 클로렐라분말, 귀리식이섬유, 레몬밤분말, 효모식품, 니코틴산아미드</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>20240658113240</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>20240658113</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>트리코바이옴MG901사균체</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>(주)메디오젠</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>덱스트린, Limosilactobacillus fermentum</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>장건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2024057720624</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>20240577206</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>보스웰리아한방복합물SA</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>상아생명과학주식회사 F1</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>기타가공품, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>관절</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>202605273108</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>20260527310</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>굴림곶감</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>현대무브 주식회사</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>사양벌꿀, 천연향신료, 버터, 잣, 곶감, 정제소금</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>20110568038376</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>20110568038</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>단백질혼합분말F3</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>주식회사 오그래 농업회사법인</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>수크랄로스, 향료, 아몬드분말, 이집트콩분말, 난소화성말토덱스트린(고시형), 유청단백분말, 식물성크림</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>20110568038377</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>20110568038</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>단백한끼 더블크런치 토피넛라떼</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>주식회사 오그래 농업회사법인</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>아몬드, 분리대두단백, 젤라틴, 기타가공품, 복합조미식품, 효소처리스테비아, 분말유크림, 기타소금, 커피, 탈지땅콩분말, 향료, 코코아분말, 탈지분유, 식물성크림, 혼합제제, 곡류가공품, 과자, 혼합제제, 비타민미네랄혼합제제, 과자, 곡류가공품, 곡류가공품</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2014015210850</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>20140152108</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>후레쉬코</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>(주)지엠생명공학</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>정제수, 보스웰리아추출물, 은행잎추출물, 감초추출액, 지치뿌리추출물, 천궁추출액, 칡발효액, 박하추출물, 목련꽃잎, 퉁퉁마디추출액</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>관절</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>20170474140102</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>20170474140</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>고로케 속재료</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>뜰방네</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>양배추, 돼지고기, 감자, 양파, 당근, 파, 당면, 마가린, 카레, 간장, 소스, 가공소금, 후추가루</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>20190478227182</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>20190478227</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>천라수 효소액</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>농업회사법인내포주식회사</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>수세미오이어린열매발효농축액, 설탕</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>효소</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
           <t>2025057771140</t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>20260911</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>20250577711</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr">
+      <c r="D634" t="inlineStr">
         <is>
           <t>콜린·엽산·이노시톨 플러스</t>
         </is>
       </c>
-      <c r="E619" t="inlineStr">
+      <c r="E634" t="inlineStr">
         <is>
           <t>기타가공품</t>
         </is>
       </c>
-      <c r="F619" t="inlineStr">
+      <c r="F634" t="inlineStr">
         <is>
           <t>주식회사 신비바이오</t>
         </is>
       </c>
-      <c r="G619" t="inlineStr">
-        <is>
-          <t>20260911</t>
-        </is>
-      </c>
-      <c r="H619" t="inlineStr">
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>20260912</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
         <is>
           <t>락티톨, 레몬과즙분말, 프락토올리고당, 이노시톨, 레몬라임향, DL-사과산, 효소처리스테비아, 오렌지향분말, 주석산수소콜린, 비타민 C(고시형), 비타민 B1염산염(고시형), 비타민 B6 염산염 혼합제제, 니코틴산아미드, 프로바이오틱스(고시형), 엽산</t>
         </is>
       </c>
-      <c r="I619" t="inlineStr">
+      <c r="I634" t="inlineStr">
         <is>
           <t>여성건강</t>
         </is>
@@ -44371,7 +45076,7 @@
         <v>18</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>17</v>
@@ -44386,7 +45091,7 @@
         <v>7</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>15</v>
@@ -44410,16 +45115,16 @@
         <v>3</v>
       </c>
       <c r="Q45" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S45" s="10" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="T45" s="8" t="n">
-        <v>618</v>
+        <v>633</v>
       </c>
     </row>
     <row r="46">
@@ -44435,7 +45140,7 @@
         <v>-107</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>-55</v>
+        <v>-54</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>-34</v>
@@ -44450,7 +45155,7 @@
         <v>-21</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>-18</v>
@@ -44474,16 +45179,16 @@
         <v>-18</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>-55</v>
+        <v>-53</v>
       </c>
       <c r="S46" s="12" t="n">
-        <v>-706</v>
+        <v>-696</v>
       </c>
       <c r="T46" s="12" t="n">
-        <v>-1284</v>
+        <v>-1269</v>
       </c>
     </row>
     <row r="47">
@@ -44563,7 +45268,7 @@
         <v>-18</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>-17</v>
@@ -44578,7 +45283,7 @@
         <v>-7</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>-15</v>
@@ -44602,16 +45307,16 @@
         <v>-3</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>-26</v>
+        <v>-28</v>
       </c>
       <c r="S48" s="12" t="n">
-        <v>-375</v>
+        <v>-385</v>
       </c>
       <c r="T48" s="12" t="n">
-        <v>-618</v>
+        <v>-633</v>
       </c>
     </row>
     <row r="49">

--- a/output/2026-09_품목신고보고현황.xlsx
+++ b/output/2026-09_품목신고보고현황.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="건강기능식품" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="일반식품" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="건강기능식품" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일반식품" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>남성건강</t>
         </is>
       </c>
     </row>
@@ -28498,7 +28498,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -37428,7 +37428,7 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>다이어트</t>
         </is>
       </c>
     </row>
@@ -42551,7 +42551,7 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -44055,7 +44055,7 @@
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>피로개선</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -47815,7 +47815,7 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>남성건강</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -49554,7 +49554,7 @@
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -49648,7 +49648,7 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -55053,7 +55053,7 @@
       </c>
       <c r="I802" t="inlineStr">
         <is>
-          <t>피로개선</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -57497,7 +57497,7 @@
       </c>
       <c r="I854" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
@@ -61829,7 +61829,7 @@
         <v>48</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D39" s="10" t="n">
         <v>62</v>
@@ -61838,25 +61838,25 @@
         <v>43</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>32</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M39" s="10" t="n">
         <v>37</v>
@@ -61868,16 +61868,16 @@
         <v>10</v>
       </c>
       <c r="P39" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q39" s="10" t="n">
         <v>12</v>
       </c>
       <c r="R39" s="10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S39" s="10" t="n">
-        <v>986</v>
+        <v>1014</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>1650</v>
@@ -61893,7 +61893,7 @@
         <v>48</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>62</v>
@@ -61902,25 +61902,25 @@
         <v>43</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>32</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L40" s="11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M40" s="11" t="n">
         <v>37</v>
@@ -61932,16 +61932,16 @@
         <v>10</v>
       </c>
       <c r="P40" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q40" s="11" t="n">
         <v>12</v>
       </c>
       <c r="R40" s="11" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>986</v>
+        <v>1014</v>
       </c>
       <c r="T40" s="11" t="n">
         <v>1650</v>
@@ -61957,16 +61957,16 @@
         <v>77</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>43</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>2</v>
@@ -61978,16 +61978,16 @@
         <v>32</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="N41" s="10" t="n">
         <v>18</v>
@@ -61996,16 +61996,16 @@
         <v>7</v>
       </c>
       <c r="P41" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q41" s="10" t="n">
         <v>15</v>
       </c>
       <c r="R41" s="10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="S41" s="10" t="n">
-        <v>1103</v>
+        <v>1129</v>
       </c>
       <c r="T41" s="8" t="n">
         <v>1921</v>
@@ -62021,22 +62021,22 @@
         <v>29</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>-2</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>0</v>
@@ -62048,10 +62048,10 @@
         <v>13</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N42" s="11" t="n">
         <v>3</v>
@@ -62066,10 +62066,10 @@
         <v>3</v>
       </c>
       <c r="R42" s="11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="S42" s="11" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="T42" s="11" t="n">
         <v>271</v>
@@ -62085,7 +62085,7 @@
         <v>78</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D43" s="10" t="n">
         <v>77</v>
@@ -62094,7 +62094,7 @@
         <v>51</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -62106,34 +62106,34 @@
         <v>39</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>25</v>
       </c>
       <c r="L43" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M43" s="10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O43" s="10" t="n">
         <v>8</v>
       </c>
       <c r="P43" s="10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q43" s="10" t="n">
         <v>17</v>
       </c>
       <c r="R43" s="10" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S43" s="10" t="n">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>1902</v>
@@ -62149,16 +62149,16 @@
         <v>1</v>
       </c>
       <c r="C44" s="12" t="n">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E44" s="11" t="n">
         <v>8</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>-2</v>
@@ -62170,34 +62170,34 @@
         <v>7</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="L44" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M44" s="11" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="O44" s="11" t="n">
         <v>1</v>
       </c>
       <c r="P44" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q44" s="11" t="n">
         <v>2</v>
       </c>
       <c r="R44" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S44" s="12" t="n">
-        <v>-22</v>
+        <v>-36</v>
       </c>
       <c r="T44" s="12" t="n">
         <v>-19</v>
@@ -62213,7 +62213,7 @@
         <v>18</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D45" s="10" t="n">
         <v>38</v>
@@ -62222,25 +62222,25 @@
         <v>20</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>17</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M45" s="10" t="n">
         <v>27</v>
@@ -62252,7 +62252,7 @@
         <v>6</v>
       </c>
       <c r="P45" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q45" s="10" t="n">
         <v>8</v>
@@ -62261,7 +62261,7 @@
         <v>39</v>
       </c>
       <c r="S45" s="10" t="n">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>888</v>
@@ -62277,7 +62277,7 @@
         <v>-60</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>-98</v>
+        <v>-92</v>
       </c>
       <c r="D46" s="12" t="n">
         <v>-39</v>
@@ -62286,19 +62286,19 @@
         <v>-31</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>-66</v>
+        <v>-65</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>-8</v>
@@ -62307,25 +62307,25 @@
         <v>-8</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>-43</v>
+        <v>-45</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O46" s="12" t="n">
         <v>-2</v>
       </c>
       <c r="P46" s="12" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q46" s="12" t="n">
         <v>-9</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>-42</v>
+        <v>-41</v>
       </c>
       <c r="S46" s="12" t="n">
-        <v>-538</v>
+        <v>-541</v>
       </c>
       <c r="T46" s="12" t="n">
         <v>-1014</v>
@@ -62405,7 +62405,7 @@
         <v>-18</v>
       </c>
       <c r="C48" s="12" t="n">
-        <v>-27</v>
+        <v>-22</v>
       </c>
       <c r="D48" s="12" t="n">
         <v>-38</v>
@@ -62414,25 +62414,25 @@
         <v>-20</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>-73</v>
+        <v>-71</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>-1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>-17</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>-27</v>
@@ -62444,7 +62444,7 @@
         <v>-6</v>
       </c>
       <c r="P48" s="12" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="Q48" s="12" t="n">
         <v>-8</v>
@@ -62453,7 +62453,7 @@
         <v>-39</v>
       </c>
       <c r="S48" s="12" t="n">
-        <v>-543</v>
+        <v>-552</v>
       </c>
       <c r="T48" s="12" t="n">
         <v>-888</v>
